--- a/tmdb_movies.xlsx
+++ b/tmdb_movies.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:V21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,42 @@
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>page</t>
+          <t>budget</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>revenue</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>runtime</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>genres</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>production_companies</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>spoken_languages</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>homepage</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tagline</t>
         </is>
       </c>
     </row>
@@ -538,7 +573,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>79.65900000000001</v>
+        <v>111.523</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -562,10 +597,41 @@
         <v>7.608</v>
       </c>
       <c r="N2" t="n">
-        <v>12292</v>
+        <v>12294</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>460000000</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2320250281</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>192</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Adventure', 'Action']</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>['20th Century Studios', 'Lightstorm Entertainment']</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>https://www.avatar.com/movies/avatar-the-way-of-water</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Return to Pandora.</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -574,7 +640,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>/AeK2MPOpYrOOgZNfFnfwp0L8tNn.jpg</t>
+          <t>/zD5v1E4joAzFvmAEytt7fM3ivyT.jpg</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -601,7 +667,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>107.608</v>
+        <v>150.651</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -625,10 +691,41 @@
         <v>7.9</v>
       </c>
       <c r="N3" t="n">
-        <v>20547</v>
+        <v>20552</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>200000000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1921847111</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>148</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>['Marvel Studios', 'Pascal Pictures', 'Columbia Pictures']</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>['English', '']</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>https://www.sonypictures.com/movies/spidermannowayhome</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>The Multiverse unleashed.</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -664,7 +761,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>181.517</v>
+        <v>254.124</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -685,13 +782,44 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.56</v>
+        <v>7.6</v>
       </c>
       <c r="N4" t="n">
-        <v>5578</v>
+        <v>5581</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>200000000</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1698863816</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>97</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>['Animation', 'Adventure', 'Comedy', 'Family']</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>['Walt Disney Pictures', 'Pixar']</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/inside-out-2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Make room for new emotions.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -727,7 +855,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>104.978</v>
+        <v>146.969</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -748,13 +876,44 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.186</v>
       </c>
       <c r="N5" t="n">
-        <v>9601</v>
+        <v>9605</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>170000000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1488732821</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>131</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>['Action', 'Drama']</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>['Skydance Media', 'Don Simpson/Jerry Bruckheimer Films', 'Paramount Pictures']</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>https://www.topgunmovie.com</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Feel the need... The need for speed.</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -790,7 +949,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>62.15</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -814,10 +973,41 @@
         <v>6.984</v>
       </c>
       <c r="N6" t="n">
-        <v>9591</v>
+        <v>9597</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>145000000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1445638421</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>114</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>['Comedy', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>['LuckyChap Entertainment', 'Heyday Films', 'NB/GG Pictures', 'Mattel', 'Warner Bros. Pictures']</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://www.barbie-themovie.com</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>She's everything. He's just Ken.</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -853,7 +1043,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>84.819</v>
+        <v>118.747</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -877,10 +1067,41 @@
         <v>7.632</v>
       </c>
       <c r="N7" t="n">
-        <v>9470</v>
+        <v>9473</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>100000000</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1362000000</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>93</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>['Animation', 'Family', 'Adventure', 'Fantasy', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Illumination', 'Nintendo']</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>https://www.uphe.com/movies/the-super-mario-bros-movie</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Not all heroes wear capes. Some wear overalls.</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -916,7 +1137,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>228.761</v>
+        <v>320.265</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -937,13 +1158,44 @@
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>7.619</v>
+        <v>7.6</v>
       </c>
       <c r="N8" t="n">
-        <v>6776</v>
+        <v>6781</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>200000000</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1338073645</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>128</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>['Action', 'Comedy', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>['Marvel Studios', 'Maximum Effort', '21 Laps Entertainment', '20th Century Studios', 'Kevin Feige Productions', 'TSG Entertainment']</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/deadpool-and-wolverine</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Come together.</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -979,7 +1231,7 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>1361.081</v>
+        <v>1623.864</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1000,13 +1252,44 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.2</v>
+        <v>7.157</v>
       </c>
       <c r="N9" t="n">
-        <v>1703</v>
+        <v>1721</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>150000000</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1044396565</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>99</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>['Animation', 'Adventure', 'Family', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>['Walt Disney Pictures', 'Walt Disney Animation Studios', 'Walt Disney Animation Studios']</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>['English', 'Italiano']</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/moana-2</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>The ocean is calling them back.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1042,7 +1325,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>126.638</v>
+        <v>147.765</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1066,10 +1349,41 @@
         <v>6.7</v>
       </c>
       <c r="N10" t="n">
-        <v>6251</v>
+        <v>6255</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>165000000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1001978080</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>147</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>['Adventure', 'Action', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>['Amblin Entertainment', 'Universal Pictures']</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://www.jurassicworld.com</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>The epic conclusion of the Jurassic era.</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1105,7 +1419,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>209.01</v>
+        <v>292.614</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1126,13 +1440,44 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>7.1</v>
+        <v>7.061</v>
       </c>
       <c r="N11" t="n">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>100000000</v>
+      </c>
+      <c r="P11" t="n">
+        <v>969280910</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>94</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>['Animation', 'Family', 'Comedy', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Illumination']</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://www.despicable.me</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>This daddy’s a baddie.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1168,7 +1513,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>56.552</v>
+        <v>79.173</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1189,13 +1534,44 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.267</v>
+        <v>7.3</v>
       </c>
       <c r="N12" t="n">
         <v>9370</v>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>200000000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>955775804</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>126</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>['Fantasy', 'Action', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>['Marvel Studios', 'Kevin Feige Productions']</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>['广州话 / 廣州話', 'English', 'Español']</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/doctor-strange-in-the-multiverse-of-madness</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Enter a new dimension of Strange.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1231,7 +1607,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>72.999</v>
+        <v>102.199</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1255,10 +1631,41 @@
         <v>8.1</v>
       </c>
       <c r="N13" t="n">
-        <v>9857</v>
+        <v>9867</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>100000000</v>
+      </c>
+      <c r="P13" t="n">
+        <v>952000000</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>181</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>['Drama', 'History']</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>['Syncopy', 'Universal Pictures', 'Atlas Entertainment', 'Breakheart Films', 'Peters Creek Entertainment']</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>['Nederlands', 'English']</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://www.universalpictures.com/movies/oppenheimer</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>The world forever changes.</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1294,7 +1701,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>35.589</v>
+        <v>49.825</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1315,13 +1722,44 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>7.302</v>
+        <v>7.3</v>
       </c>
       <c r="N14" t="n">
         <v>3680</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>85000000</v>
+      </c>
+      <c r="P14" t="n">
+        <v>940203765</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>87</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>['Animation', 'Comedy', 'Family', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Illumination']</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://www.minionsmovie.com/</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>A villain will rise.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1353,7 +1791,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>9.869999999999999</v>
+        <v>9.746</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1380,7 +1818,34 @@
         <v>105</v>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>200000000</v>
+      </c>
+      <c r="P15" t="n">
+        <v>902540935</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>178</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>['Drama', 'War']</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>['Bona Film Group', 'Shanghai Film Group', 'DF Pictures', 'Alibaba Pictures Group', 'China Film Group Corporation', 'Distribution Workshop', 'Huaxia Film Distribution', 'Just Creative Studio']</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>['普通话', 'English']</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Do they fall out of the goddamn sky?</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1416,7 +1881,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>58.598</v>
+        <v>82.03700000000001</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1440,10 +1905,41 @@
         <v>7.1</v>
       </c>
       <c r="N16" t="n">
-        <v>6684</v>
+        <v>6686</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>250000000</v>
+      </c>
+      <c r="P16" t="n">
+        <v>859102154</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>162</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>['Marvel Studios']</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>['English', 'Français', '', 'Español', '']</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://wakandaforevertickets.com</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Forever.</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1479,7 +1975,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>63.091</v>
+        <v>88.327</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1503,10 +1999,41 @@
         <v>8</v>
       </c>
       <c r="N17" t="n">
-        <v>7159</v>
+        <v>7160</v>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>250000000</v>
+      </c>
+      <c r="P17" t="n">
+        <v>845600000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>150</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Adventure', 'Action']</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>['Marvel Studios', 'Kevin Feige Productions']</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/guardians-of-the-galaxy-volume-3</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Once more with feeling.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1538,7 +2065,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>6.964</v>
+        <v>8.307</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1565,8 +2092,31 @@
         <v>147</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
-      </c>
+        <v>59000000</v>
+      </c>
+      <c r="P18" t="n">
+        <v>822049668</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>128</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>['Drama', 'Comedy', 'Fantasy']</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>['Alibaba Pictures Group', 'Tianjin Maoyan Media', 'Beijing Big Bowl Entertainment Culture Media', 'Beijing Culture', 'Beijing Cheering Times Culture &amp; Entertainment', 'Shanghai Ruyi Film &amp; TV Production']</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="b">
@@ -1601,7 +2151,7 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>29.744</v>
+        <v>41.642</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1622,13 +2172,44 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7.368</v>
+        <v>7.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6406</v>
+        <v>6407</v>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>250000000</v>
+      </c>
+      <c r="P19" t="n">
+        <v>774153024</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>163</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>['Action', 'Thriller', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>['EON Productions', 'Metro-Goldwyn-Mayer']</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>['Español', 'English', 'Italiano', 'Français', 'Pусский']</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://www.007.com/no-time-to-die/</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>The mission that changes everything begins…</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1664,7 +2245,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>55.633</v>
+        <v>77.886</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1688,10 +2269,41 @@
         <v>7.7</v>
       </c>
       <c r="N20" t="n">
-        <v>10663</v>
+        <v>10665</v>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>185000000</v>
+      </c>
+      <c r="P20" t="n">
+        <v>772319315</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>177</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>['Crime', 'Mystery', 'Thriller']</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>['6th &amp; Idaho Motion Picture Company', 'Dylan Clark Productions', 'DC Films', 'Warner Bros. Pictures']</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://www.thebatman.com</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Unmask the truth.</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1727,7 +2339,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>39.69</v>
+        <v>55.566</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1751,10 +2363,41 @@
         <v>6.422</v>
       </c>
       <c r="N21" t="n">
-        <v>7773</v>
+        <v>7775</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>250000000</v>
+      </c>
+      <c r="P21" t="n">
+        <v>760900000</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>119</v>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>['Fantasy', 'Action', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>['Marvel Studios', 'Kevin Feige Productions']</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/thor-love-and-thunder</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>The one is not the only.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/tmdb_movies.xlsx
+++ b/tmdb_movies.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V21"/>
+  <dimension ref="A1:V101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>111.523</v>
+        <v>137.751</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>['Science Fiction', 'Adventure', 'Action']</t>
+          <t>['Ciencia ficción', 'Aventura', 'Acción']</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -625,12 +625,12 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://www.avatar.com/movies/avatar-the-way-of-water</t>
+          <t>https://www.20thcenturystudiosla.com/peliculas/avatar-el-camino-del-agua</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Return to Pandora.</t>
+          <t>Esta familia es nuestro fuerte.</t>
         </is>
       </c>
     </row>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>150.651</v>
+        <v>159.864</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -704,7 +704,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>['Action', 'Adventure', 'Science Fiction']</t>
+          <t>['Acción', 'Aventura', 'Ciencia ficción']</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://www.sonypictures.com/movies/spidermannowayhome</t>
+          <t>https://www.sonypictures.com.mx/movies/spider-man-sin-camino-casa</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>The Multiverse unleashed.</t>
+          <t>Un gran poder conlleva una gran responsabilidad.</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>254.124</v>
+        <v>334.444</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>7.6</v>
+        <v>7.56</v>
       </c>
       <c r="N4" t="n">
-        <v>5581</v>
+        <v>5583</v>
       </c>
       <c r="O4" t="n">
         <v>200000000</v>
@@ -794,11 +794,11 @@
         <v>1698863816</v>
       </c>
       <c r="Q4" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>['Animation', 'Adventure', 'Comedy', 'Family']</t>
+          <t>['Animación', 'Aventura', 'Comedia', 'Familia']</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://movies.disney.com/inside-out-2</t>
+          <t>https://www.disneylatino.com/peliculas/intensamente-2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Make room for new emotions.</t>
+          <t>Hagan espacio para nuevas emociones.</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>146.969</v>
+        <v>184.313</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>['Action', 'Drama']</t>
+          <t>['Acción', 'Drama']</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -905,14 +905,10 @@
           <t>['English']</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>https://www.topgunmovie.com</t>
-        </is>
-      </c>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Feel the need... The need for speed.</t>
+          <t>Siente la necesidad... La necesidad de velocidad.</t>
         </is>
       </c>
     </row>
@@ -949,7 +945,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>87.01000000000001</v>
+        <v>121.814</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -982,11 +978,11 @@
         <v>1445638421</v>
       </c>
       <c r="Q6" t="n">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>['Comedy', 'Adventure']</t>
+          <t>['Comedia', 'Aventura']</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1001,12 +997,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://www.barbie-themovie.com</t>
+          <t>https://www.warnerbroslatino.com/es-mx/peliculas/barbie</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>She's everything. He's just Ken.</t>
+          <t>Ella lo es todo. Él es solo Ken.</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1039,7 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>118.747</v>
+        <v>163.339</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1067,7 +1063,7 @@
         <v>7.632</v>
       </c>
       <c r="N7" t="n">
-        <v>9473</v>
+        <v>9476</v>
       </c>
       <c r="O7" t="n">
         <v>100000000</v>
@@ -1076,11 +1072,11 @@
         <v>1362000000</v>
       </c>
       <c r="Q7" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>['Animation', 'Family', 'Adventure', 'Fantasy', 'Comedy']</t>
+          <t>['Animación', 'Familia', 'Aventura', 'Fantasía', 'Comedia']</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1095,12 +1091,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://www.uphe.com/movies/the-super-mario-bros-movie</t>
+          <t>https://www.universalpictures.com.mx/micro/super-mario-bros</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Not all heroes wear capes. Some wear overalls.</t>
+          <t>No todos los héroes usan capa. Algunos usan manos.</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1133,7 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>320.265</v>
+        <v>368.88</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1161,7 +1157,7 @@
         <v>7.6</v>
       </c>
       <c r="N8" t="n">
-        <v>6781</v>
+        <v>6782</v>
       </c>
       <c r="O8" t="n">
         <v>200000000</v>
@@ -1174,7 +1170,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>['Action', 'Comedy', 'Science Fiction']</t>
+          <t>['Acción', 'Comedia', 'Ciencia ficción']</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1189,12 +1185,12 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://www.marvel.com/movies/deadpool-and-wolverine</t>
+          <t>https://www.disneylatino.com/peliculas/deadpool-&amp;-wolverine</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Come together.</t>
+          <t>Acabaron juntos.</t>
         </is>
       </c>
     </row>
@@ -1252,10 +1248,10 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>7.157</v>
+        <v>7.153</v>
       </c>
       <c r="N9" t="n">
-        <v>1721</v>
+        <v>1727</v>
       </c>
       <c r="O9" t="n">
         <v>150000000</v>
@@ -1268,7 +1264,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>['Animation', 'Adventure', 'Family', 'Comedy']</t>
+          <t>['Animación', 'Aventura', 'Familia', 'Comedia']</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1281,14 +1277,10 @@
           <t>['English', 'Italiano']</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>https://movies.disney.com/moana-2</t>
-        </is>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr">
         <is>
-          <t>The ocean is calling them back.</t>
+          <t>El océano los está llamando.</t>
         </is>
       </c>
     </row>
@@ -1325,7 +1317,7 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>147.765</v>
+        <v>140.184</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1362,7 +1354,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>['Adventure', 'Action', 'Science Fiction']</t>
+          <t>['Aventura', 'Acción', 'Ciencia ficción']</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1377,12 +1369,12 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://www.jurassicworld.com</t>
+          <t>https://www.universalpictures-latam.com/micro/jurassic-world-dominion</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>The epic conclusion of the Jurassic era.</t>
+          <t>La épica conclusión de la era Jurásica.</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1411,7 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>292.614</v>
+        <v>404.22</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1456,7 +1448,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>['Animation', 'Family', 'Comedy', 'Science Fiction']</t>
+          <t>['Animación', 'Familia', 'Comedia', 'Ciencia ficción']</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1471,14 +1463,10 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://www.despicable.me</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>This daddy’s a baddie.</t>
-        </is>
-      </c>
+          <t>https://www.universalpictures-latam.com/micro/dm4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="b">
@@ -1513,7 +1501,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>79.173</v>
+        <v>91.89400000000001</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1534,10 +1522,10 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>7.3</v>
+        <v>7.268</v>
       </c>
       <c r="N12" t="n">
-        <v>9370</v>
+        <v>9371</v>
       </c>
       <c r="O12" t="n">
         <v>200000000</v>
@@ -1550,7 +1538,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>['Fantasy', 'Action', 'Adventure']</t>
+          <t>['Fantasía', 'Acción', 'Aventura']</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1563,14 +1551,10 @@
           <t>['广州话 / 廣州話', 'English', 'Español']</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>https://www.marvel.com/movies/doctor-strange-in-the-multiverse-of-madness</t>
-        </is>
-      </c>
+      <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Enter a new dimension of Strange.</t>
+          <t>Entra en una nueva dimensión de Strange.</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1591,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>102.199</v>
+        <v>143.079</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1628,10 +1612,10 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>8.1</v>
+        <v>8.071</v>
       </c>
       <c r="N13" t="n">
-        <v>9867</v>
+        <v>9870</v>
       </c>
       <c r="O13" t="n">
         <v>100000000</v>
@@ -1644,7 +1628,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>['Drama', 'History']</t>
+          <t>['Drama', 'Historia']</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1659,12 +1643,12 @@
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://www.universalpictures.com/movies/oppenheimer</t>
+          <t>https://www.universalpictures-latam.com/micro/oppenheimer</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>The world forever changes.</t>
+          <t>Descubre la intensa paradoja del enigmático hombre que debe arriesgarse a destruir el mundo para salvarlo.</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1685,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>49.825</v>
+        <v>69.755</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1725,7 +1709,7 @@
         <v>7.3</v>
       </c>
       <c r="N14" t="n">
-        <v>3680</v>
+        <v>3681</v>
       </c>
       <c r="O14" t="n">
         <v>85000000</v>
@@ -1738,7 +1722,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>['Animation', 'Comedy', 'Family', 'Adventure']</t>
+          <t>['Animación', 'Comedia', 'Familia', 'Aventura']</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1751,14 +1735,10 @@
           <t>['English']</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>https://www.minionsmovie.com/</t>
-        </is>
-      </c>
+      <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr">
         <is>
-          <t>A villain will rise.</t>
+          <t>Prepárate para descubrir la historia jamás contada de un niño de 12 años.</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1771,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>9.746</v>
+        <v>13.644</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1828,7 +1808,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>['Drama', 'War']</t>
+          <t>['Drama', 'Bélica']</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1842,11 +1822,7 @@
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Do they fall out of the goddamn sky?</t>
-        </is>
-      </c>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="b">
@@ -1881,7 +1857,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>82.03700000000001</v>
+        <v>101.328</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1918,7 +1894,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>['Action', 'Adventure', 'Science Fiction']</t>
+          <t>['Acción', 'Aventura', 'Ciencia ficción']</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1933,12 +1909,12 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://wakandaforevertickets.com</t>
+          <t>https://disneylatino.com/peliculas/pantera-negra-wakanda-por-siempre</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Forever.</t>
+          <t>Por siempre.</t>
         </is>
       </c>
     </row>
@@ -1975,7 +1951,7 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>88.327</v>
+        <v>123.658</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1996,10 +1972,10 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>7.953</v>
       </c>
       <c r="N17" t="n">
-        <v>7160</v>
+        <v>7162</v>
       </c>
       <c r="O17" t="n">
         <v>250000000</v>
@@ -2012,7 +1988,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>['Science Fiction', 'Adventure', 'Action']</t>
+          <t>['Ciencia ficción', 'Aventura', 'Acción']</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2027,12 +2003,12 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://www.marvel.com/movies/guardians-of-the-galaxy-volume-3</t>
+          <t>https://www.disneylatino.com/peliculas/guardianes-de-la-galaxia-vol-3</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Once more with feeling.</t>
+          <t>Listos para el último baile.</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2041,7 @@
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>8.307</v>
+        <v>6.258</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2102,7 +2078,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>['Drama', 'Comedy', 'Fantasy']</t>
+          <t>['Drama', 'Comedia', 'Fantasía']</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2175,7 +2151,7 @@
         <v>7.4</v>
       </c>
       <c r="N19" t="n">
-        <v>6407</v>
+        <v>6408</v>
       </c>
       <c r="O19" t="n">
         <v>250000000</v>
@@ -2188,7 +2164,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>['Action', 'Thriller', 'Adventure']</t>
+          <t>['Acción', 'Suspense', 'Aventura']</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2203,12 +2179,12 @@
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://www.007.com/no-time-to-die/</t>
+          <t>https://www.universalpictures-latam.com/micro/no-time-to-die</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>The mission that changes everything begins…</t>
+          <t>La misión que cambia todo, comienza...</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2221,7 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>77.886</v>
+        <v>104.7</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2266,10 +2242,10 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>7.7</v>
+        <v>7.658</v>
       </c>
       <c r="N20" t="n">
-        <v>10665</v>
+        <v>10667</v>
       </c>
       <c r="O20" t="n">
         <v>185000000</v>
@@ -2278,11 +2254,11 @@
         <v>772319315</v>
       </c>
       <c r="Q20" t="n">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>['Crime', 'Mystery', 'Thriller']</t>
+          <t>['Crimen', 'Misterio', 'Suspense']</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2297,12 +2273,12 @@
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://www.thebatman.com</t>
+          <t>https://www.warnerbroslatino.com/es-mx/peliculas/batman</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>Unmask the truth.</t>
+          <t>Desenmascara la verdad.</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2315,7 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>55.566</v>
+        <v>66.104</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2376,7 +2352,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>['Fantasy', 'Action', 'Comedy']</t>
+          <t>['Fantasía', 'Acción', 'Comedia']</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2389,16 +2365,7364 @@
           <t>['English']</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>https://www.marvel.com/movies/thor-love-and-thunder</t>
-        </is>
-      </c>
+      <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr">
         <is>
-          <t>The one is not the only.</t>
-        </is>
-      </c>
+          <t>Él no es el único.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="b">
+        <v>0</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>/uKb22E0nlzr914bA9KyA5CVCOlV.jpg</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[18, 10749, 14]</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>402431</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Wicked</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>La historia de cómo una mujer de piel verde esmeralda se convierte en la Malvada Bruja del Oeste; largometraje basado en el musical de Broadway.</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>330.427</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>/1ZSVA2pNpc89C07RDgsR6p0GMs7.jpg</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2024-11-20</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Wicked</t>
+        </is>
+      </c>
+      <c r="L22" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>6.901</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1818</v>
+      </c>
+      <c r="O22" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="P22" t="n">
+        <v>728145850</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>162</v>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>['Drama', 'Romance', 'Fantasy']</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Marc Platt Productions']</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://www.wickedmovie.com</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Everyone deserves the chance to fly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="b">
+        <v>0</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>/xXHZeb1yhJvnSHPzZDqee0zfMb6.jpg</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[28, 12, 80]</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>385128</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Domic Toretto lleva una vida tranquila, lejos de todo, con Letty y su hijo, el pequeño Brian. el peligro está siempre al acecho. Esta vez, esta amenaza obligará a Domic Toretto a enfrentarse a los pecados de su pasado para salvar a los que más quiere. Su equipo se reúne de nuevo para detener un plan que conmocionó al mundo, liderado por el mejor piloto y el mayor asesino que han encontrado: Jakob, el hermano abandonado de Domic.</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>44.644</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>/TX1T3c3CDBN0y8iDNvlQbtiA5Z.jpg</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2021-05-19</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Rápidos y furiosos 9</t>
+        </is>
+      </c>
+      <c r="L23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7288</v>
+      </c>
+      <c r="O23" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P23" t="n">
+        <v>726229501</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>143</v>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Crime']</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>['Original Film', 'One Race', 'Perfect Storm Entertainment', 'Universal Pictures', 'Roth-Kirschenbaum Films']</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>['English', 'Français', 'Deutsch', 'Español']</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://www.uphe.com/movies/f9-the-fast-saga</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Not all blood is family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="b">
+        <v>0</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>/xOMo8BRK7PfcJv9JCnx7s5hj0PX.jpg</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[878, 12]</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>693134</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dune: Part Two</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sigue la mítica jornada de Paul Atreides mientras se une con Chani y los Fremen en su camino hacia la venganza contra los conspiradores que destruyeron a su familia. Enfrentado a una elección entre el amor de su vida y el destino del universo conocido, Paul se esfuerza por prevenir un terrible futuro que solo él puede prever.</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>174.334</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>/xCHmhHeO7aOCMlzcNukGH6Q7EiD.jpg</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Duna: Parte dos</t>
+        </is>
+      </c>
+      <c r="L24" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>6327</v>
+      </c>
+      <c r="O24" t="n">
+        <v>190000000</v>
+      </c>
+      <c r="P24" t="n">
+        <v>714444358</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>167</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>['Legendary Pictures']</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>https://www.dunemovie.com</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Long live the fighters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="b">
+        <v>0</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>/4XM8DUTQb3lhLemJC51Jx4a2EuA.jpg</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[28, 80, 53]</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>385687</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Fast X</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>A través de varias misiones y contra lo imposible, Dom Toretto y su familia han sido más astutos y más rápidos que todos los enemigos se le han cruzado en su camino. Ahora se enfrentan a su enemigo más letal: una amenaza aterradora que surge de las sombras del pasado que está alimentado de una venganza sangrienta, y está decidido a destruir a su familia y destruir todo, y a cualquier persona, a los que Dom ama.</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>189.243</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>/3P9QvWVN02Etn4kYGC702WVoXEb.jpg</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Rápidos y furiosos X</t>
+        </is>
+      </c>
+      <c r="L25" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5790</v>
+      </c>
+      <c r="O25" t="n">
+        <v>340000000</v>
+      </c>
+      <c r="P25" t="n">
+        <v>704709660</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>142</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>['Action', 'Crime', 'Thriller']</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Original Film', 'One Race', 'Perfect Storm Entertainment']</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>['English', 'Español']</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>https://fastxmovie.com</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>The end of the road begins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="b">
+        <v>0</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>/cVh8Af7a9JMOJl75ML3Dg2QVEuq.jpg</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[12, 10751, 16]</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>762509</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Mufasa: The Lion King</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>La historia se cuenta en flashbacks y presenta a Mufasa como un cachorro huérfano, perdido y solo hasta que conoce a un simpático león llamado Taka, heredero de un linaje real. Este encuentro casual pone en marcha un viaje de un extraordinario grupo de inadaptados que buscan su destino. Y sus vínculos se pondrán a prueba mientras trabajan juntos para escapar de un enemigo amenazador y letal.</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>2049.75</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>/dmw74cWIEKaEgl5Dv3kUTcCob6D.jpg</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Mufasa: El rey león</t>
+        </is>
+      </c>
+      <c r="L26" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N26" t="n">
+        <v>1446</v>
+      </c>
+      <c r="O26" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P26" t="n">
+        <v>700197856</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>118</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>['Adventure', 'Family', 'Animation']</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>['Walt Disney Pictures']</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/mufasa-the-lion-king</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>The story of an orphan who would be king.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="b">
+        <v>0</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>/kVd3a9YeLGkoeR50jGEXM6EqseS.jpg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[16, 28, 12, 878]</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>569094</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spider-Man: Across the Spider-Verse</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Después de reunirse con Gwen Stacy, Miles Morales, el amigable Spider-Man del vecindario de tiempo completo de Brooklyn, es catapultado a través del Multiverso, donde se encuentra con un equipo de Spider-People encargado de proteger su existencia. Pero cuando los héroes chocan sobre cómo manejar una nueva amenaza, Miles se enfrenta a las otras arañas y debe redefinir lo que significa ser un héroe para poder salvar a las personas que más ama.</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>145.068</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>/37WcNMgNOMxdhT87MFl7tq7FM1.jpg</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Spider-Man: A través del Spider-Verso</t>
+        </is>
+      </c>
+      <c r="L27" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N27" t="n">
+        <v>7342</v>
+      </c>
+      <c r="O27" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="P27" t="n">
+        <v>690897910</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>140</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>['Animation', 'Action', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>['Columbia Pictures', 'Sony Pictures Animation', 'Lord Miller', 'Pascal Pictures', 'Arad Productions', 'Marvel Entertainment']</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>['English', 'हिन्दी', 'Italiano', 'Español']</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>https://www.sonypictures.com/movies/spidermanacrossthespiderverse</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>It's how you wear the mask that matters.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="b">
+        <v>0</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>/ihBzrXY1R8MDnT1JMWatrMjqUY6.jpg</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[28, 35, 9648]</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>602666</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>唐人街探案3</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>11.885</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>/nbGzncqTJw94LHisdEXKC1dFc3J.jpg</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2021-02-12</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>唐人街探案3</t>
+        </is>
+      </c>
+      <c r="L28" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N28" t="n">
+        <v>85</v>
+      </c>
+      <c r="O28" t="n">
+        <v>117000000</v>
+      </c>
+      <c r="P28" t="n">
+        <v>686257563</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>136</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>['Action', 'Comedy', 'Mystery']</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>['Beijing Yitong Legend Films', 'China Film Co-Production Corp.', 'As One Production', 'Wanda Pictures']</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>['日本語', '普通话']</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="b">
+        <v>0</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>/hcWXnOL7ScXpFQVjJruYUODeQxX.jpg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[9648, 35, 53, 36]</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1066298</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>满江红</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Un peón intenta deshacerse de un ministro traidor, Qin Hui, cuando dirige un ejército a la frontera para mantener conversaciones con una misión jurchen.</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>8.147</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>/aijuMcDt5MoavJnlxMd7rKVEdZb.jpg</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2023-01-22</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Full River Red</t>
+        </is>
+      </c>
+      <c r="L29" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5.901</v>
+      </c>
+      <c r="N29" t="n">
+        <v>147</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>673556758</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>157</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>['Mystery', 'Comedy', 'Thriller', 'History']</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>['Huanxi Media Group', 'Edko Films', 'Emperor Motion Pictures']</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="b">
+        <v>0</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>/yOm993lsJyPmBodlYjgpPwBjXP9.jpg</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[35, 10751, 14]</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>787699</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Wonka</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Willy Wonka, repleto de ideas y decidido a cambiar el mundo con un delicioso bocado a la vez, es una prueba de que las mejores cosas de la vida comienzan con un sueño y, si tienes la suerte de conocer a Willy Wonka, todo es posible.</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>73.376</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>/6eHcR7zwvNSvkOl9jbctU0lvZQ1.jpg</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Wonka</t>
+        </is>
+      </c>
+      <c r="L30" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7.095</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3769</v>
+      </c>
+      <c r="O30" t="n">
+        <v>125000000</v>
+      </c>
+      <c r="P30" t="n">
+        <v>632302312</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>117</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>['Comedy', 'Family', 'Fantasy']</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>['Warner Bros. Pictures', 'Village Roadshow Pictures', 'The Roald Dahl Story Company', 'Heyday Films', 'Domain Entertainment']</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>https://www.wonkamovie.com</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Every good thing in this world started with a dream.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="b">
+        <v>0</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>/mMA2YNddowV8MZtxpbn0a7Yilum.jpg</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[10752, 36, 28, 18]</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>928123</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>长津湖之水门桥</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Secuela de "The Battle at Lake Changjin" que se centra en los soldados del CPV (Chinese People's Volunteers) en una nueva misión crucial para vencer a las tropas norteamericanas.</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>13.956</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>/4KNTMdGPpklyQWC8D95kBxQkC8P.jpg</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>La batalla del lago Changjin II</t>
+        </is>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N31" t="n">
+        <v>70</v>
+      </c>
+      <c r="O31" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P31" t="n">
+        <v>626203271</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>149</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>['War', 'History', 'Action', 'Drama']</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>['Bona Film Group', 'Distribution Workshop', 'China Film Group Corporation', 'Alibaba Pictures Group', 'Huaxia Film Distribution', 'Just Creative Studio', 'Mandrill Visual Effects']</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>['English', '普通话']</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="b">
+        <v>0</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>/94cS0mzODEoNIXFT7nhPcI8V4IJ.jpg</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[878]</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>842675</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>流浪地球2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tras descubrir que el Sol se apaga rápidamente, la humanidad construye enormes motores para mover la Tierra a un nuevo sistema solar. En una carrera contra el tiempo, valientes héroes asumen la misión de salvar a la humanidad de la extinción.</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>34.251</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>/dCDAPDbySxYewfSzWGvQssy04sW.jpg</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2023-01-22</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>La Tierra errante II</t>
+        </is>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="N32" t="n">
+        <v>594</v>
+      </c>
+      <c r="O32" t="n">
+        <v>73800000</v>
+      </c>
+      <c r="P32" t="n">
+        <v>615023132</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>173</v>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>['Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>['China Film Group Corporation', 'Guo Fan Culture and Media']</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>['普通话', 'English', 'Français', '日本語', 'Português', 'Pусский', 'Español']</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>https://trinitycineasia.com/in-cinemas/the-wandering-earth-ii/</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="b">
+        <v>0</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>/lLh39Th5plbrQgbQ4zyIULsd0Pp.jpg</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[28, 12, 878]</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>823464</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Godzilla x Kong: The New Empire</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Una aventura cinematográfica completamente nueva, que enfrentará al todopoderoso Kong y al temible Godzilla contra una colosal amenaza desconocida escondida dentro de nuestro mundo. La nueva y épica película profundizará en las historias de estos titanes, sus orígenes y los misterios de Isla Calavera y más allá, mientras descubre la batalla mítica que ayudó a forjar a estos seres extraordinarios y los unió a la humanidad para siempre.</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>149.531</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>/2YqZ6IyFk7menirwziJvfoVvSOh.jpg</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Godzilla y Kong: El nuevo imperio</t>
+        </is>
+      </c>
+      <c r="L33" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>4073</v>
+      </c>
+      <c r="O33" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="P33" t="n">
+        <v>571750016</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>115</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>['Legendary Pictures']</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>https://www.godzillaxkongmovie.com</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Rise together or fall alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="b">
+        <v>0</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>/znUYFf0Sez5lUmxPr3Cby7TVJ6c.jpg</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[12, 10751, 14, 10749]</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>447277</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>The Little Mermaid</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Ariel, la más joven de las hijas del rey Tritón y la más desafiante, anhela saber más sobre el mundo más allá del mar y, mientras visita la superficie, se enamora del apuesto príncipe Eric. Con las sirenas prohibidas para interactuar con los humanos, Ariel hace un trato con la malvada bruja del mar, Ursula, que le da la oportunidad de experimentar la vida en la tierra, pero finalmente pone en peligro su vida y la corona de su padre.</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>78.751</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>/mdszPVnIY7cWgbgJ8zbwu1PiU5V.jpg</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2023-05-18</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>La sirenita</t>
+        </is>
+      </c>
+      <c r="L34" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3000</v>
+      </c>
+      <c r="O34" t="n">
+        <v>297000000</v>
+      </c>
+      <c r="P34" t="n">
+        <v>569626289</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>135</v>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>['Adventure', 'Family', 'Fantasy', 'Romance']</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>['Walt Disney Pictures', 'Lucamar Productions', 'Marc Platt Productions']</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/the-little-mermaid-2023</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Watch and you'll see, some day I'll be, part of your world!</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="b">
+        <v>0</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>/TFTfzrkX8L7bAKUcch6qLmjpLu.jpg</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[28, 12]</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>575264</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mission: Impossible - Dead Reckoning Part One</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Ethan Hunt y su equipo del FMI, se embarcan en su misión más peligrosa hasta la fecha: localizar, antes de que caiga en las manos equivocadas, una nueva y terrorífica arma que amenaza a toda la humanidad. En esta tesitura, y con unas fuerzas oscuras del pasado de Ethan acechando, comienza una carrera mortal alrededor del mundo en la que está en juego el control del futuro y el destino del planeta. Enfrentado a un enemigo misterioso y todopoderoso, Ethan se ve obligado a considerar que nada puede anteponerse a su misión, ni siquiera las vidas de aquellos que más le importan.</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>92.709</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>/83sGKvCv2T2CulYbd40Aeduc7n2.jpg</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2023-07-08</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Misión: Imposible - Sentencia mortal parte uno</t>
+        </is>
+      </c>
+      <c r="L35" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>7.531</v>
+      </c>
+      <c r="N35" t="n">
+        <v>4052</v>
+      </c>
+      <c r="O35" t="n">
+        <v>291000000</v>
+      </c>
+      <c r="P35" t="n">
+        <v>567535383</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>164</v>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>['Paramount Pictures', 'Skydance Media', 'TC Productions']</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>['Français', 'English', 'Italiano', 'Pусский']</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>https://www.paramountmovies.com/movies/mission-impossible-dead-reckoning</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>We all share the same fate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="b">
+        <v>0</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>/kYgQzzjNis5jJalYtIHgrom0gOx.jpg</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[16, 10751, 28, 35]</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1011985</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kung Fu Panda 4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Po se está preparando para convertirse en el líder espiritual de su Valle de la Paz, pero también necesita a alguien que ocupe su lugar como Guerrero Dragón. Como tal, entrenará a un nuevo practicante de kung fu para el lugar y se encontrará con un villano llamado Camaleón que evoca villanos del pasado.</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>170.597</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>/zS8BSQdbOesql0EWbs17kPvLoAT.jpg</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2024-03-02</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Kung Fu Panda 4</t>
+        </is>
+      </c>
+      <c r="L36" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>7.073</v>
+      </c>
+      <c r="N36" t="n">
+        <v>2986</v>
+      </c>
+      <c r="O36" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="P36" t="n">
+        <v>548040835</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>94</v>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>['Animation', 'Family', 'Action', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>['DreamWorks Animation']</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>https://www.dreamworks.com/movies/kung-fu-panda-4</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="b">
+        <v>0</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>/3FVe3OAdgz060JaxIAaUl5lo6cx.jpg</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[16, 28, 14, 53]</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>635302</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>劇場版「鬼滅の刃」無限列車編</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tanjiro Kamado y sus amigos de la Compañía de Cazadores de Demonios (Kimetsu no Yaiba Corps), se unen con uno de los mejores espadachines de la compañía, Kyojuro Rengoku, para investigar una misteriosa serie de desapariciones que han ocurrido dentro del “Tren Infinito”. Poco saben que Enmu, uno de los miembros de las Doce Lunas Demoníacas, también está a bordo y les ha preparado una trampa.</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>62.606</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>/8t29MfbEkEZixjVbjRkqI5NyFR4.jpg</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2020-10-16</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Demon Slayer: Mugen Train La película</t>
+        </is>
+      </c>
+      <c r="L37" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="N37" t="n">
+        <v>4018</v>
+      </c>
+      <c r="O37" t="n">
+        <v>15700000</v>
+      </c>
+      <c r="P37" t="n">
+        <v>507119058</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>117</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>['Animation', 'Action', 'Fantasy', 'Thriller']</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>['ufotable', 'Aniplex', 'Shueisha', 'TOHO']</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>['日本語']</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>https://demonslayer-anime.com</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>With your blade, bring an end to the nightmare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="b">
+        <v>0</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>/vIgyYkXkg6NC2whRbYjBD7eb3Er.jpg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[878, 28, 12]</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>580489</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Venom: Let There Be Carnage</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Eddie Brock y su simbionte Venom todavía están intentando descubrir cómo vivir juntos cuando un preso que está en el corredor de la muerte se infecta con un simbionte propio.</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>74.563</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>/b0j9rHYpRML7dKm5xw9e97HTDJF.jpg</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Venom: Carnage Liberado</t>
+        </is>
+      </c>
+      <c r="L38" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10516</v>
+      </c>
+      <c r="O38" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="P38" t="n">
+        <v>506863592</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>97</v>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Action', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>['Columbia Pictures', 'Pascal Pictures', 'Matt Tolmach Productions', 'Arad Productions']</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>['Español', 'English']</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>https://www.venom.movie</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>It’s time to meet Carnage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="b">
+        <v>0</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>/uuw0PRR4sgGi1IV4CYYpEYtez9y.jpg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[12, 35, 18]</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>960876</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>hi</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>डंकी</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cuando sus amigos de Punyab no logran obtener la visa para irse al Reino Unido, un soldado retirado los guía en un arriesgado viaje para emigrar ilegalmente.</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>12.63</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>/slyetWArMvWg6cyXz2kr2OAmYP6.jpg</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2023-12-21</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Destino: Londres</t>
+        </is>
+      </c>
+      <c r="L39" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>77</v>
+      </c>
+      <c r="O39" t="n">
+        <v>239000000</v>
+      </c>
+      <c r="P39" t="n">
+        <v>501000000</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>159</v>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>['Adventure', 'Comedy', 'Drama']</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>['Red Chillies Entertainment', 'Rajkumar Hirani Films', 'Jio Studios']</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>['हिन्दी', 'ਪੰਜਾਬੀ']</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>A Soldier's journey to keep a promise</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="b">
+        <v>0</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>/6YInbRTk39ckuLYFmUgBCKcKNjb.jpg</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[16, 35, 10751, 14, 10749]</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>976573</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Elemental</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>En una ciudad en la que conviven el fuego, el agua, la tierra y el aire, una joven llena de fuego y un tipo que fluye descubrirán lo mucho que tienen en común.</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>104.218</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>/d79DeKDCgFOM23O8Dr6MELZVooY.jpg</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2023-06-14</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Elementos</t>
+        </is>
+      </c>
+      <c r="L40" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N40" t="n">
+        <v>4684</v>
+      </c>
+      <c r="O40" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P40" t="n">
+        <v>496444308</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>102</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>['Animation', 'Comedy', 'Family', 'Fantasy', 'Romance']</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>['Walt Disney Pictures', 'Pixar']</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/elemental</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Opposites react.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="b">
+        <v>0</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>/jr8tSoJGj33XLgFBy6lmZhpGQNu.jpg</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[16, 12, 14, 35, 10751]</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>315162</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Puss in Boots: The Last Wish</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>El audaz forajido Gato con Botas descubre que su pasión por el peligro y su desprecio por la seguridad le han pasado factura. El Gato ha quemado ocho de sus nueve vidas, aunque ha perdido la cuenta por el camino. Recuperar esas vidas hará que el Gato con Botas emprenda su mayor búsqueda hasta ahora; la mítica Estrella de los Deseos.</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>/b5Jb7GoQaqIXy4VEdnQa0UrQZI.jpg</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2022-12-07</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Gato con Botas: El último deseo</t>
+        </is>
+      </c>
+      <c r="L41" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="N41" t="n">
+        <v>8025</v>
+      </c>
+      <c r="O41" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="P41" t="n">
+        <v>484700000</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>103</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>['Animation', 'Adventure', 'Fantasy', 'Comedy', 'Family']</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>['DreamWorks Animation']</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>['English', 'Español']</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>https://www.dreamworks.com/movies/puss-in-boots-the-last-wish</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Every legend comes to an end.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="b">
+        <v>0</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>/9IEYCg2Sxk72QdNNcvbbCMelalu.jpg</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[18, 35, 28]</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1229349</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>热辣滚烫</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Hace años que Le Ying (interpretada por Jia Ling) vive en casa de sus padres, sin dirección en la vida y sin hacer nada en particular. Después de graduarse de la universidad y trabajar solo por un tiempo, Le Ying decide aislarse de la sociedad. Un día, después de varias vueltas del destino, decide vivir la vida de otra manera. Al aventurarse con cautela en el mundo exterior, Le Ying conoce al entrenador de boxeo Hao Kun (Lei Jia Yin). Justo cuando cree que la vida está a punto de dar un giro positivo, los desafíos que debe enfrentar superan ampliamente lo que había imaginado, y su vibrante vida acaba de comenzar…</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>18.308</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>/3JJSLb9nQutbMRY9lwpMVoKEBhm.jpg</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Yolo - solo se vive una vez</t>
+        </is>
+      </c>
+      <c r="L42" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N42" t="n">
+        <v>74</v>
+      </c>
+      <c r="O42" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="P42" t="n">
+        <v>480600000</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>129</v>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>['Drama', 'Comedy', 'Action']</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>['Alibaba Pictures Group', 'Beijing Big Bowl Entertainment Culture Media', 'China Film Group Corporation', 'New Classics Media', 'Tencent Penguin Pictures']</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>To win, at least once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="b">
+        <v>0</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>/vZG7PrX9HmdgL5qfZRjhJsFYEIA.jpg</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[28, 878, 12]</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>912649</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Venom: The Last Dance</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Eddie y Venom están huyendo. Perseguidos por sus dos mundos, el dúo se ve obligado a tomar una decisión devastadora que bajará el telón en un último baile entre Venom y Eddie.</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>701.816</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>/8F74DwgFxTIBNtbqSLjR7zWmnHh.jpg</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2024-10-22</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Venom: El último baile</t>
+        </is>
+      </c>
+      <c r="L43" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>6.783</v>
+      </c>
+      <c r="N43" t="n">
+        <v>2915</v>
+      </c>
+      <c r="O43" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="P43" t="n">
+        <v>478103649</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>109</v>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>['Action', 'Science Fiction', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>['Columbia Pictures', 'Pascal Pictures', 'Matt Tolmach Productions', 'Hutch Parker Entertainment', 'Arad Productions']</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>https://venom.movie</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>'Til death do they part.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="b">
+        <v>0</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>/m8JTwHFwX7I7JY5fPe4SjqejWag.jpg</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[28, 12, 878]</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>640146</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Ant-Man and the Wasp: Quantumania</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Los superhéroes Scott Lang y Hope van Dyne regresan para continuar sus aventuras como Ant-Man y Wasp. Con los padres de Hope, Hank Pym y Janet van Dyne, y con la hija de Scott, Cassie Lang, la familia explora el Reino Quántico, interactúa con extrañas criaturas y se embarca en una aventura que los hará ir más allá de lo que creían posible.</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>44.142</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>/lKHy0ntGPdQeFwvNq8gK1D0anEr.jpg</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2023-02-15</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Ant-Man and the Wasp: Quantumania</t>
+        </is>
+      </c>
+      <c r="L44" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>6.298</v>
+      </c>
+      <c r="N44" t="n">
+        <v>5158</v>
+      </c>
+      <c r="O44" t="n">
+        <v>388369742</v>
+      </c>
+      <c r="P44" t="n">
+        <v>476071180</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>125</v>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>['Marvel Studios', 'Kevin Feige Productions']</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/ant-man-and-the-wasp-quantumania</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Witness the beginning of a new dynasty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="b">
+        <v>0</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>/vH0IXldpTM8J3MCT35khoeUMb5E.jpg</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[35]</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>1299537</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>12.562</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>/dFNJOjtKD9ypSHciXY6JRgK24Pw.jpg</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2024-07-13</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>抓娃娃</t>
+        </is>
+      </c>
+      <c r="L45" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>7</v>
+      </c>
+      <c r="N45" t="n">
+        <v>53</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>473859800</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>133</v>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>['Comedy']</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>['海口西虹胡同影视文化有限公司', 'Tianjin Maoyan Weiying Culture Media', 'Fun Age Pictures', 'Shanghai Ruyi Film &amp; TV Production', 'Alibaba Pictures Group', 'Horgos Coloroom Pictures', 'China Film Group Corporation', '长影时代传媒股份有限公司', '西虹市影视文化', 'New Classics Media', '海南乐镜影视文化传媒有限公司', 'Zhejiang Hengdian Film Production', 'Tencent Penguin Pictures', '蜃景影视文化传播（海口）有限公司', '安徽文逸影视文化传媒有限公司', '吉林省石头剪刀布传媒有限公司', 'Wanda Pictures', 'Youku']</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="b">
+        <v>0</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>/zOpe0eHsq0A2NvNyBbtT6sj53qV.jpg</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[28, 878, 35, 10751]</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>939243</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog 3</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sonic, Knuckles y Tails se reúnen para enfrentarse a un nuevo y poderoso adversario, Shadow, un misterioso villano con poderes nunca antes vistos. Con sus habilidades superadas en todos los sentidos, el Equipo Sonic debe buscar una alianza improbable con la esperanza de detener a Shadow y proteger el planeta.</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>1866.273</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>/3aDWCRXLYOCuxjrjiPfLd79tcI6.jpg</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2024-12-19</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Sonic 3: La Película</t>
+        </is>
+      </c>
+      <c r="L46" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>7.752</v>
+      </c>
+      <c r="N46" t="n">
+        <v>2011</v>
+      </c>
+      <c r="O46" t="n">
+        <v>122000000</v>
+      </c>
+      <c r="P46" t="n">
+        <v>472518457</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>110</v>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>['Action', 'Science Fiction', 'Comedy', 'Family']</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>['Paramount Pictures', 'Original Film', 'Marza Animation Planet', 'SEGA', 'Blur Studio', 'SEGA of America']</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>https://www.sonicthehedgehogmovie.com</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>New adventure. New rival.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="b">
+        <v>0</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>/inJjDhCjfhh3RtrJWBmmDqeuSYC.jpg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[28, 878, 12]</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>399566</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Godzilla vs. Kong</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>En un momento en que los monstruos caminan por la Tierra, la lucha de la humanidad por su futuro coloca a Godzilla y Kong en un curso de colisión que verá a las dos fuerzas más poderosas de la naturaleza en el planeta enfrentarse en una batalla espectacular para las edades. Mientras Monarch se embarca en una peligrosa misión en un terreno inexplorado y descubre pistas sobre los orígenes de los Titanes, una conspiración humana amenaza con borrar a las criaturas, tanto buenas como malas, de la faz de la tierra para siempre.</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>43.742</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>/yJTk4eqQd9Yo5REpFbTSOMkbSgn.jpg</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2021-03-24</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Godzilla vs Kong</t>
+        </is>
+      </c>
+      <c r="L47" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="N47" t="n">
+        <v>10096</v>
+      </c>
+      <c r="O47" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P47" t="n">
+        <v>470116094</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>114</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>['Action', 'Science Fiction', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>['Legendary Pictures']</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>https://www.warnerbros.com/movies/godzilla-vs-kong</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>One will fall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="b">
+        <v>0</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>/ch8rKF1a5WXFDcxi2AKfmnaMBk7.jpg</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[18, 35, 12]</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1228891</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>飞驰人生2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>7.824</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>/mJGPPKMsYTxvkAIu4SbAtP2PCef.jpg</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>飞驰人生2</t>
+        </is>
+      </c>
+      <c r="L48" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N48" t="n">
+        <v>56</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>468924000</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>121</v>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>['Drama', 'Comedy', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>['Shanghai PMF Media', 'Tao Piao Piao', 'Maoyan Entertainment', 'Bona Film Group', 'China Film Group Corporation', 'Fun Age Pictures', 'Zhejiang Hengdian Film Production', 'Shanghai Ruyi Film &amp; TV Production', '上海电影（集团）有限公司', 'Weibo Corporation']</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="b">
+        <v>0</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>/IRN1JuNwr1VKp88Dscgja2uR8H.jpg</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[10752, 36, 18, 28]</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>508935</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>八佰</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>En 1937, ochocientos soldados chinos luchan bajo el asedio en Shanghai, desde un almacén en medio del campo de batalla, completamente rodeados por el ejército japonés.</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>15.13</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>/8kwsdVNBTZyNQ8s4LFqR10fOvk1.jpg</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>2020-08-14</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Los 800</t>
+        </is>
+      </c>
+      <c r="L49" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N49" t="n">
+        <v>274</v>
+      </c>
+      <c r="O49" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="P49" t="n">
+        <v>461421559</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>147</v>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>['War', 'History', 'Drama', 'Action']</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>['Beijing Diqi Yinxiang Entertainment', 'Huayi Brothers Pictures', 'Beijing Enlight Pictures', 'Tencent Pictures', 'South Australian Film Corporation', 'Huaxia Film Distribution']</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>['普通话', 'English', '日本語']</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>https://cmc-pictures.com/the-eight-hundred/</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Based on the true story of one of the greatest battles of WWII.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="b">
+        <v>0</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>/g9aQu5QADrJcDGm3KBKGYmSJ6Ki.jpg</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[878, 35, 18]</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>801803</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>6.302</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>/uLfT4oOj0Cp2XuUCDWZpvFMeSmE.jpg</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>2022-07-29</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>独行月球</t>
+        </is>
+      </c>
+      <c r="L50" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>6.882</v>
+      </c>
+      <c r="N50" t="n">
+        <v>85</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>460300583</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>122</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Comedy', 'Drama']</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>['Fun Age Pictures']</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="b">
+        <v>0</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>/bHeUgZKqduubnNl8GshjrpHS9lF.jpg</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[28, 12, 18]</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>558449</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Gladiator II</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Años después de presenciar la muerte del venerado héroe Maximus a manos de su tío, Lucius se ve obligado a ingresar al Coliseo después de que su hogar fuera conquistado por los emperadores tiránicos que ahora dirigen Roma con mano de hierro. Con rabia en su corazón y el futuro del Imperio en juego, Lucius debe mirar a su pasado para encontrar fuerza y ​​honor para devolver la gloria de Roma a su pueblo.</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>616.14</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>/fbcs5AxrdXwyj1b8bGGMgC9kXrM.jpg</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Gladiador II</t>
+        </is>
+      </c>
+      <c r="L51" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2920</v>
+      </c>
+      <c r="O51" t="n">
+        <v>310000000</v>
+      </c>
+      <c r="P51" t="n">
+        <v>458718000</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>148</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Drama']</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>['Paramount Pictures', 'Scott Free Productions', 'Lucy Fisher/Douglas Wick Productions']</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>https://www.gladiator.movie</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Prepare to be entertained.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="b">
+        <v>0</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>/xi1VSt3DtkevUmzCx2mNlCoDe74.jpg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[35, 14, 27]</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>917496</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Beetlejuice Beetlejuice</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Después de una tragedia familiar, tres generaciones de la familia Deetz regresan a su hogar en Winter River. La vida de Lydia, que aún sigue atormentada por Beetlejuice, da un vuelco cuando su hija adolescente, Astrid, abre accidentalmente el portal al más allá.</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>84.188</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>/9utRLSrJ7Jn9YoeUJpeNPCWeI6t.jpg</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>2024-09-04</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Beetlejuice Beetlejuice</t>
+        </is>
+      </c>
+      <c r="L52" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>7.067</v>
+      </c>
+      <c r="N52" t="n">
+        <v>2336</v>
+      </c>
+      <c r="O52" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="P52" t="n">
+        <v>451100435</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>105</v>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>['Comedy', 'Fantasy', 'Horror']</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>['Warner Bros. Pictures', 'Geffen Pictures', 'Plan B Entertainment', 'Tim Burton Productions', 'Tommy Harper Productions', 'Domain Entertainment']</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>https://www.beetlejuicemovie.com</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>The ghost with the most is back.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="b">
+        <v>0</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>/2vFuG6bWGyQUzYS9d69E5l85nIz.jpg</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[878, 12, 28]</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>667538</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Transformers: Rise of the Beasts</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Una aventura alrededor del mundo con los Autobots que introducirá una nueva facción de Transformers - los Maximals - en la batalla existente en la Tierra entre Autobots y Decepticons.</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>141.19</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>/peIB7KBBrqW0JsCLQBt9ChEtZ7m.jpg</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Transformers: El despertar de las bestias</t>
+        </is>
+      </c>
+      <c r="L53" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="N53" t="n">
+        <v>4814</v>
+      </c>
+      <c r="O53" t="n">
+        <v>195000000</v>
+      </c>
+      <c r="P53" t="n">
+        <v>441381193</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>127</v>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Adventure', 'Action']</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>['Skydance Media', 'Paramount Pictures', 'di Bonaventura Pictures', 'Bay Films', 'New Republic Pictures', 'DeSanto/Murphy Productions', 'Hasbro']</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>['', 'Español', 'English']</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>https://www.paramountmovies.com/movies/transformers-rise-of-the-beasts</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Unite or fall.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="b">
+        <v>0</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>/7I6VUdPj6tQECNHdviJkUHD2u89.jpg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[28, 53, 80]</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>603692</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>John Wick: Chapter 4</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>John Wick descubre un camino para derrotar a La Mesa. Pero antes de poder ganar su libertad, Wick deberá enfrentarse a un nuevo enemigo con poderosas alianzas en todo el mundo; y contra las fuerzas que convierten a viejos amigos en enemigos.</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>127.893</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>/mj2Z9HnRSIEk3n7yVPoOY4Uzzfh.jpg</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>2023-03-22</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>John Wick 4</t>
+        </is>
+      </c>
+      <c r="L54" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>7.721</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6870</v>
+      </c>
+      <c r="O54" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="P54" t="n">
+        <v>440157245</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>170</v>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>['Action', 'Thriller', 'Crime']</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>['Thunder Road', '87Eleven', 'Studio Babelsberg', 'Lionsgate']</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>['العربية', '广州话 / 廣州話', 'English', 'Français', 'Deutsch', '日本語', 'Latin', 'Pусский', 'Español']</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>https://johnwick.movie/film/john-wick-4</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>No way back, one way out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="b">
+        <v>0</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>/7S0bXv3BqCuPfImKRf5kkmBVYZR.jpg</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[28, 12, 14]</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>572802</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Aquaman and the Lost Kingdom</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Black Manta, todavía impulsado por la necesidad de vengar la muerte de su padre y ejerciendo el poder del mítico Tridente Negro, no se detendrá ante nada para acabar con Aquaman de una vez por todas. Para derrotarlo, Aquaman debe recurrir a su hermano encarcelado Orm, el ex rey de la Atlántida, para forjar una alianza improbable con el fin de salvar al mundo de una destrucción irreversible.</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>77.93000000000001</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>/a0QwtpUNIKjOlNoOVmk7d2LFnQW.jpg</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2023-12-20</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Aquaman y el reino perdido</t>
+        </is>
+      </c>
+      <c r="L55" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>6.617</v>
+      </c>
+      <c r="N55" t="n">
+        <v>2977</v>
+      </c>
+      <c r="O55" t="n">
+        <v>205000000</v>
+      </c>
+      <c r="P55" t="n">
+        <v>439381226</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>124</v>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Fantasy']</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>['Warner Bros. Pictures', 'The Safran Company', 'Atomic Monster', 'DC Films', 'Domain Entertainment']</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>['한국어/조선말', '普通话', 'English']</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>https://www.aquamanmovie.com</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>The tide is turning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="b">
+        <v>0</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>/zxWAv1A34kdYslBi4ekMDtgIGUt.jpg</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[28, 12, 14]</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>566525</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Shang-Chi and the Legend of the Ten Rings</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Shang-Chi debe enfrentarse al pasado que pensó que había dejado atrás cuando se ve atraído por la red de la misteriosa organización de los Diez Anillos.</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>71.59699999999999</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>/9VqajJXm29uprSaxOcEh7O0d6E9.jpg</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>2021-09-01</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Shang-Chi y la leyenda de los Diez Anillos</t>
+        </is>
+      </c>
+      <c r="L56" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>7.528</v>
+      </c>
+      <c r="N56" t="n">
+        <v>9577</v>
+      </c>
+      <c r="O56" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="P56" t="n">
+        <v>432243292</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>132</v>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Fantasy']</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>['Marvel Studios']</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>['English', '普通话']</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/shang-chi-and-the-legend-of-the-ten-rings</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>You can't outrun your destiny.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="b">
+        <v>0</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>/ddygUzXBHGqnlBPcUI70ih7QOW0.jpg</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[10402]</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>715904</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Metallica: WorldWired Tour - Live in Manchester, England - June 18, 2019</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>/ehM3D3KKo2OUxVVBFif1OJbtqGP.jpg</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>2020-06-08</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metallica: WorldWired Tour - Live in Manchester, England - June 18, 2019</t>
+        </is>
+      </c>
+      <c r="L57" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>426900000</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>150</v>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>['Music']</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>https://www.metallica.com/events/2019-06-18-manchester-england.html</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="b">
+        <v>0</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>/eAIHqfS3kXm7kZl4j7ZBfdegyEz.jpg</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[53, 28, 80]</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>38700</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bad Boys for Life</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Es la tercera y (supuestamente) última parte de Dos policías rebeldes, con sus dos protagonistas originales, Will Smith y Martin Lawrence. Acción y humor al estilo noventero con una trama random: los agentes, ya maduritos, vuelven a reunirse porque un criminal ha puesto precio a sus cabezas. Ya no dirige Michael Bay, sino los belgas Adil El Arbi y Bilall Fallah.</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>62.972</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>/5XR7Pbo8qdwdpOIsFtWJOEiOJD6.jpg</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>2020-01-15</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Bad Boys para Siempre</t>
+        </is>
+      </c>
+      <c r="L58" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>7.135</v>
+      </c>
+      <c r="N58" t="n">
+        <v>8352</v>
+      </c>
+      <c r="O58" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="P58" t="n">
+        <v>426505244</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>124</v>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>['Thriller', 'Action', 'Crime']</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>['Columbia Pictures', '2.0 Entertainment', 'Don Simpson/Jerry Bruckheimer Films', 'Overbrook Entertainment']</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>['English', 'Español']</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>https://www.sonypictures.com/movies/badboysforlife</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Ride together. Die together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="b">
+        <v>0</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>/ztiFxuG0gC6wQ8y7JZFYbCQyN4Y.jpg</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[16, 10751, 10402, 35]</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>438695</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Sing 2</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Buster Moon y su elenco de animales artistas se preparan para lanzar un deslumbrante espectáculo escénico en la capital mundial del entretenimiento. Solo hay un problema: debe convencer a la estrella de rock más solitaria del mundo de unirse a ellos.</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>73.711</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>/9iIDsw7RJHYU94z7k4mbYP5IlYT.jpg</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>2021-12-01</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Sing 2: ¡Ven y Canta de Nuevo!</t>
+        </is>
+      </c>
+      <c r="L59" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>7.853</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4460</v>
+      </c>
+      <c r="O59" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="P59" t="n">
+        <v>408402685</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>110</v>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>['Animation', 'Family', 'Music', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Illumination']</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>https://www.illumination.com/movie/sing-2/</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Where will your dreams take you?</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="b">
+        <v>0</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>/jYEW5xZkZk2WTrdbMGAPFuBqbDc.jpg</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[878, 12]</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>438631</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Dune</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Paul Atreides, un joven brillante y talentoso nacido en un gran destino más allá de su entendimiento, debe viajar al planeta más peligroso del universo para asegurar el futuro de su familia y de su pueblo.</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>118.972</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>/szcew6yyjcDvaL0isaPBk2e3nkF.jpg</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>2021-09-15</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Duna</t>
+        </is>
+      </c>
+      <c r="L60" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N60" t="n">
+        <v>13227</v>
+      </c>
+      <c r="O60" t="n">
+        <v>165000000</v>
+      </c>
+      <c r="P60" t="n">
+        <v>407573628</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>155</v>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>['Legendary Pictures']</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>['普通话', 'English']</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>https://www.dunemovie.com/</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>It begins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="b">
+        <v>0</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>/zGLHX92Gk96O1DJvLil7ObJTbaL.jpg</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[14, 12]</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>338953</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Fantastic Beasts: The Secrets of Dumbledore</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>El profesor Albus Dumbledore sabe que el poderoso mago oscuro Gellert Grindelward se está moviendo para ganar control del mundo mágico. Incapaz de detenerlo por sí solo, le confía al magizoologista Newt Scamander que lidere un intrépido grupo de magos, brujas y un valiente panadero muggle en una aventura peligrosa donde se encontrarán con nuevas y viejas bestias mientras chocan con los seguidores de Grindelwald.</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>48.423</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>/yOeuJdwag4bAlnvgrdweRoiuXGC.jpg</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>2022-04-06</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Animales Fantásticos 3: Los Secretos de Dumbledore</t>
+        </is>
+      </c>
+      <c r="L61" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>6.647</v>
+      </c>
+      <c r="N61" t="n">
+        <v>4611</v>
+      </c>
+      <c r="O61" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P61" t="n">
+        <v>407200000</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>142</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>['Fantasy', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>['Warner Bros. Pictures', 'Heyday Films']</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>https://www.fantasticbeasts.com</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Return to the magic.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="b">
+        <v>0</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>/fwrqW8Lp5VQuppFrODd4iJ8LySE.jpg</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[28, 12]</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>335787</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Uncharted</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>El astuto ladrón Nathan Drake es reclutado por el experimentado cazador de tesoros Victor “Sully” Sullivan para recuperar una fortuna perdida por Ferdinand Magellan hace 500 años. Lo que comienza como un trabajo de atraco para el dúo se convierte en una carrera trotamundos y nudillos blancos para alcanzar el premio antes que el despiadado Moncada, quien cree que él y su familia son los legítimos herederos. Si Nate y Sully pueden descifrar las pistas y resolver uno de los misterios más antiguos del mundo, pueden encontrar un tesoro de $5 mil millones y tal vez incluso al hermano perdido de Nate... pero solo si pueden aprender a trabajar juntos.</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>96.09699999999999</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>/6hlI9Ea1O4IeJ2cj7OiNinqg8Qd.jpg</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>2022-02-10</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Uncharted: Fuera del mapa</t>
+        </is>
+      </c>
+      <c r="L62" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
+        <v>6.918</v>
+      </c>
+      <c r="N62" t="n">
+        <v>6140</v>
+      </c>
+      <c r="O62" t="n">
+        <v>120000000</v>
+      </c>
+      <c r="P62" t="n">
+        <v>407141258</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>116</v>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>['Columbia Pictures', 'Atlas Entertainment', 'PlayStation Productions', 'Arad Productions']</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>['English', 'Español']</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>https://www.unchartedmovie.com</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Fortune favors the bold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="b">
+        <v>0</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>/xuLA0pii2IMJW2puT7EvJtgpg0H.jpg</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[28, 12, 10751, 35]</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>675353</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog 2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Después de establecerse en Green Hills, Sonic está ansioso por demostrar que tiene lo que se necesita para ser un verdadero héroe. Su prueba llega cuando el Dr. Robotnik regresa, esta vez con un nuevo compañero, Knuckles, en busca de una esmeralda que tiene el poder de destruir civilizaciones. Sonic se une a su propio compañero, Tails, y juntos se embarcan en un viaje por el mundo para encontrar la esmeralda antes de que caiga en las manos equivocadas.</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>165.078</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>/sJiHVM0A3OXDVxl4Z6a7ihMPHfm.jpg</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>2022-03-30</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Sonic 2: La Película</t>
+        </is>
+      </c>
+      <c r="L63" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
+        <v>7.48</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5361</v>
+      </c>
+      <c r="O63" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="P63" t="n">
+        <v>405421518</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>123</v>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Family', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>['Original Film', 'Blur Studio', 'Marza Animation Planet', 'Paramount Pictures', 'SEGA', 'SEGA of America']</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://www.paramountmovies.com/movies/sonic-the-hedgehog-2</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Welcome to the next level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="b">
+        <v>0</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>/3q01ACG0MWm0DekhvkPFCXyPZSu.jpg</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[28, 35, 80, 53, 12]</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>573435</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Bad Boys: Ride or Die</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tras escuchar falsas acusaciones sobre su excapitán y mentor Mike y Marcus deciden investigar el asunto incluso volverse los más buscados de ser necesarios</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>222.002</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>/5jI2vEHJReAx8iFDmhC2O3yW37w.jpg</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>2024-06-05</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Bad Boys: Hasta la muerte</t>
+        </is>
+      </c>
+      <c r="L64" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" t="n">
+        <v>7.386</v>
+      </c>
+      <c r="N64" t="n">
+        <v>2776</v>
+      </c>
+      <c r="O64" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="P64" t="n">
+        <v>404547819</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>115</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>['Action', 'Comedy', 'Crime', 'Thriller', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>['Westbrook', 'Columbia Pictures', 'Don Simpson/Jerry Bruckheimer Films', '2.0 Entertainment']</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>https://www.badboys.movie</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Miami's finest are now its most wanted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="b">
+        <v>0</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>/c6H7Z4u73ir3cIoCteuhJh7UCAR.jpg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[878, 28, 12]</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>524434</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Eternals</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Los Eternos son una raza inmortal de héroes de elite que han vivido en secreto en la Tierra durante años para proteger y formar a las civilizaciones. Una tragedia inesperada los obliga a salir de las sombras para reunirse y enfrentarse al enemigo más antiguo del hombre: los Desviantes.</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>53.862</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>/wPZ5n5LlzFFdO5lFJbi2qmaE6w7.jpg</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>2021-11-03</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Eternals</t>
+        </is>
+      </c>
+      <c r="L65" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N65" t="n">
+        <v>8428</v>
+      </c>
+      <c r="O65" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P65" t="n">
+        <v>402064899</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>156</v>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Action', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>['Marvel Studios']</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>['العربية', 'English', 'हिन्दी', 'Latin', 'Español']</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/eternals</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>In the beginning...</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="b">
+        <v>0</v>
+      </c>
+      <c r="B66" t="inlineStr"/>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[10751, 10402]</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>1425681</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Lyna Live From Buenos Aires: Gran Rex</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>0.028</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>/tRSUucmADPSPrGPpIgG7Qx3N22p.jpg</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>2023-01-01</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Lyna Live From Buenos Aires: Gran Rex</t>
+        </is>
+      </c>
+      <c r="L66" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="P66" t="n">
+        <v>400000000</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>90</v>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>['Family', 'Music']</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>THE MOST FOLLOWED ARGENTINE IN THE WORLD SOLD OUT 11 PERFORMANCES AT THE GRAN REX, MAKING HISTORY FOR THE COUNTRY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="b">
+        <v>0</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>/fypydCipcWDKDTTCoPucBsdGYXW.jpg</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>[878, 12, 28]</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>653346</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kingdom of the Planet of the Apes</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>300 años después del reinado de César, un nuevo líder tiránico construye su imperio esclavizando a otros clanes de primates, un joven simio llamado Noa emprende un viaje desgarrador que lo hará cuestionar todo lo que sabía sobre el pasado y tomar decisiones que definirán el futuro tanto de simios como humanos.</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>146.974</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>/kkFn3KM47Qq4Wjhd8GuFfe3LX27.jpg</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>2024-05-08</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>El planeta de los simios: Nuevo reino</t>
+        </is>
+      </c>
+      <c r="L67" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="N67" t="n">
+        <v>3583</v>
+      </c>
+      <c r="O67" t="n">
+        <v>160000000</v>
+      </c>
+      <c r="P67" t="n">
+        <v>397378150</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>145</v>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Adventure', 'Action']</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>['20th Century Studios', 'Oddball Entertainment', 'Jason T. Reed Productions']</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>https://www.20thcenturystudios.com/movies/kingdom-of-the-planet-of-the-apes</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>No one can stop the reign.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="b">
+        <v>0</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>/bQXAqRx2Fgc46uCVWgoPz5L5Dtr.jpg</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>[28, 12, 878]</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>436270</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Black Adam</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Casi 5,000 años después de obtener los poderes supremos de los antiguos dioses, y de ser encarcelado igual de rápido, Teth Adam se libera de su tumba terrenal, listo para desatar su peculiar forma de justicia en el mundo moderno.</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>53.191</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>/moDLTCdLx38kMhN53KOTw0LdWMh.jpg</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>2022-10-19</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Black Adam</t>
+        </is>
+      </c>
+      <c r="L68" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="N68" t="n">
+        <v>6443</v>
+      </c>
+      <c r="O68" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P68" t="n">
+        <v>393452111</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>125</v>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>['New Line Cinema', 'Flynn Picture Company', 'DC Films', 'Seven Bucks Productions', 'Warner Bros. Pictures']</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>https://www.dc.com/BlackAdam</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>The world needed a hero. It got Black Adam.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="b">
+        <v>0</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>/nY09lw5kPyXRqKHkrqddkcZGM5r.jpg</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>[28, 35]</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>923192</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>这个杀手不太冷静</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>3.795</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>/yN2VMJrgyklapBOn2EXmH8DQKck.jpg</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>2022-02-01</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>这个杀手不太冷静</t>
+        </is>
+      </c>
+      <c r="L69" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="N69" t="n">
+        <v>40</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0</v>
+      </c>
+      <c r="P69" t="n">
+        <v>393014816</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>109</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>['Action', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>['New Classics Media', 'Slinky Town Pictures', 'Tianjin Yuewen Media']</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>https://www.wellgousa.com/films/too-cool-to-kill</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="b">
+        <v>0</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>/5mzr6JZbrqnqD8rCEvPhuCE5Fw2.jpg</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>[28, 878, 27]</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>615656</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Meg 2: The Trench</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Un equipo de investigación inicia una misión que va a explorar las profundidades más abismales del mar. Pero su viaje se convierte en caos cuando un malévolo operativo minero amenaza su misión y los obliga a librar una batalla de alto riesgo por la supervivencia. Enfrentados a colosales Megalodones y a implacables saqueadores medioambientales, nuestros héroes deben correr más rápido, ser más astutos y nadar a mayor velocidad que sus despiadados depredadores en una trepidante carrera contra el tiempo.</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>73.271</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>/mBgynPDplmo5JTY9VfGqY35OjDu.jpg</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>2023-08-02</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Megalodón 2: El gran abismo</t>
+        </is>
+      </c>
+      <c r="L70" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N70" t="n">
+        <v>3520</v>
+      </c>
+      <c r="O70" t="n">
+        <v>129000000</v>
+      </c>
+      <c r="P70" t="n">
+        <v>384056482</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>116</v>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>['Action', 'Science Fiction', 'Horror']</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>['Apelles Entertainment', 'Warner Bros. Pictures', 'di Bonaventura Pictures', 'CMC Pictures', 'Onaroll Productions', 'DF Pictures']</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>https://www.themeg.movie</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Back for seconds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="b">
+        <v>0</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>/35z8hWuzfFUZQaYog8E9LsXW3iI.jpg</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>[12, 28]</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>335977</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Indiana Jones and the Dial of Destiny</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>El arqueólogo Indiana Jones deberá emprender otra aventura contra el tiempo para intentar recuperar un dial legendario que puede cambiar el curso de la historia. Acompañado por su ahijada, Jones pronto se encuentra enfrentándose a Jürgen Voller, un ex nazi que trabaja para la NASA.</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>67.693</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>/mHbjhqR277tW0uiCOf5QZpJATGf.jpg</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>2023-06-25</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Indiana Jones y el dial del destino</t>
+        </is>
+      </c>
+      <c r="L71" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" t="n">
+        <v>6.561</v>
+      </c>
+      <c r="N71" t="n">
+        <v>3560</v>
+      </c>
+      <c r="O71" t="n">
+        <v>294700000</v>
+      </c>
+      <c r="P71" t="n">
+        <v>383963057</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>155</v>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>['Adventure', 'Action']</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>['Lucasfilm Ltd.']</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>['English', 'العربية', 'Español', 'Deutsch', 'Français']</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/indiana-jones-and-the-dial-of-destiny</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>His final adventure will be his greatest.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="b">
+        <v>0</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>/dq18nCTTLpy9PmtzZI6Y2yAgdw5.jpg</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>[28, 12, 878]</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>497698</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Natasha Romanoff, también conocida como Black Widow, se enfrenta a lo más oscuro de sus cuentas pendientes cuando surge una peligrosa conspiración que tiene lazos con su pasado. Perseguida por una fuerza que no se detendrá ante nada para derribarla, debe lidiar con su historia como espía y con las relaciones rotas que dejó a su paso mucho antes de convertirse en parte de los Vengadores.</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>57.154</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>/iKntUTTLxUgizTe3jFcGLuHc84c.jpg</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>2021-07-07</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Black Widow</t>
+        </is>
+      </c>
+      <c r="L72" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N72" t="n">
+        <v>10363</v>
+      </c>
+      <c r="O72" t="n">
+        <v>200000000</v>
+      </c>
+      <c r="P72" t="n">
+        <v>379751131</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>134</v>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>['Action', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>['Marvel Studios']</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>['English', 'Pусский']</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>https://www.marvel.com/movies/black-widow</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Her world. Her secrets. Her legacy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="b">
+        <v>0</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>/58D6ZAvOKxlHjyX9S8qNKSBE9Y.jpg</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>[28, 53]</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>718821</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Twisters</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Kate Carter, una ex cazadora de tormentas perseguida por un devastador encuentro con un tornado durante, es llamada por su amigo Javi de regreso a las llanuras abiertas para probar un nuevo e innovador sistema de seguimiento. Allí, se cruza con la encantadora e imprudente superestrella de las redes sociales Tyler Owens y su estridente equipo. A medida que la temporada de tormentas se intensifica, se desatarán fenómenos aterradores nunca antes vistos, y Kate, Tyler y sus equipos competidores se encuentran de lleno en el camino de múltiples sistemas de tormentas que convergen sobre el centro de Oklahoma en la lucha de sus vidas.</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>88.16</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>/4UWDVI6IleoKl9T6wHbHcqd5zAX.jpg</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>2024-07-10</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Tornados</t>
+        </is>
+      </c>
+      <c r="L73" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N73" t="n">
+        <v>2244</v>
+      </c>
+      <c r="O73" t="n">
+        <v>155000000</v>
+      </c>
+      <c r="P73" t="n">
+        <v>370962265</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>123</v>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>['Action', 'Thriller']</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Warner Bros. Pictures', 'Amblin Entertainment', 'Domain Entertainment']</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>https://www.twisters-movie.com</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Chase. Ride. Survive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="b">
+        <v>0</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>/2C3CdVzINUm5Cm1lrbT2uiRstwX.jpg</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>[28, 14, 10752]</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>856289</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>封神第一部：朝歌风云</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Una epopeya de fantasía oriental que recrea las prolongadas guerras míticas entre humanos, inmortales y monstruos que tuvieron lugar hace más de tres mil años.</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>58.346</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>/p1p3KHxTeKYvZG3KTJYDYSVygJs.jpg</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>封神第一部：朝歌风云</t>
+        </is>
+      </c>
+      <c r="L74" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" t="n">
+        <v>7.075</v>
+      </c>
+      <c r="N74" t="n">
+        <v>398</v>
+      </c>
+      <c r="O74" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="P74" t="n">
+        <v>369081777</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>148</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>['Action', 'Fantasy', 'War']</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>['Beijing Culture', 'Century Changshengtian Film', 'Tencent Penguin Pictures', 'Maoyan Entertainment', 'Huaxia Film Distribution']</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="b">
+        <v>0</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>/yY76zq9XSuJ4nWyPDuwkdV7Wt0c.jpg</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>[28, 53, 878]</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>577922</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tenet</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Una acción épica que gira en torno al espionaje internacional, los viajes en el tiempo y la evolución, en la que un agente secreto debe evitar la Tercera Guerra Mundial.</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>48.791</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>/8W7GrgHc9FdfFhExGLSD8woZaSd.jpg</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>2020-08-22</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Tenet</t>
+        </is>
+      </c>
+      <c r="L75" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N75" t="n">
+        <v>10082</v>
+      </c>
+      <c r="O75" t="n">
+        <v>205000000</v>
+      </c>
+      <c r="P75" t="n">
+        <v>365304105</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>150</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>['Action', 'Thriller', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>['Warner Bros. Pictures', 'Syncopy']</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>['English', 'Eesti']</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>https://www.tenetfilm.com/</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Time runs out.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="b">
+        <v>0</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>/8yPSYhooj8nyBbmV3GVdLDwuE7e.jpg</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>[18, 10749]</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1079091</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>It Ends with Us</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Una mujer atraviesa las tumultuosas etapas de una relación abusiva. Tras mudarse a la ciudad de Boston después de la universidad, decide iniciar su propio negocio como florista y se enamora de un joven neurocirujano.</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>82.015</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>/e0S9UXyuHE1JAoHZmyqRJISpyoS.jpg</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Romper el círculo</t>
+        </is>
+      </c>
+      <c r="L76" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" t="n">
+        <v>7.085</v>
+      </c>
+      <c r="N76" t="n">
+        <v>1454</v>
+      </c>
+      <c r="O76" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="P76" t="n">
+        <v>350993761</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>131</v>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>['Drama', 'Romance']</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>['Columbia Pictures', 'Wayfarer Studios', 'Saks Picture Company']</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>https://www.itendswithus.movie</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>We break the pattern or the pattern breaks us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="b">
+        <v>0</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>/iJaSpQNZ8GsqVDWfbCXmyZQXZ5l.jpg</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>[27, 878]</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>945961</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Alien: Romulus</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Mientras exploran en las profundidades de una estación espacial abandonada, un grupo de jóvenes colonizadores del espacio se encuentran cara a cara con la forma de vida más aterradora del universo.</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>226.648</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>/tbmIvv6p7zkd5eWRQyquCzmuogp.jpg</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Alien: Romulus</t>
+        </is>
+      </c>
+      <c r="L77" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="N77" t="n">
+        <v>3368</v>
+      </c>
+      <c r="O77" t="n">
+        <v>80000000</v>
+      </c>
+      <c r="P77" t="n">
+        <v>350865342</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>119</v>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>['Horror', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>['20th Century Studios', 'Scott Free Productions', 'Brandywine Productions']</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>https://www.20thcenturystudios.com/movies/alien-romulus</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>In space, no one can hear you.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="b">
+        <v>0</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>/PsyMMWKOyMVjTZBiyhNebyHDsQ.jpg</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>[18, 35]</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1147596</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>第二十条</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>4.728</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>/uHMMNbYJKmqSPcCR7DmixOJR49X.jpg</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>第二十条</t>
+        </is>
+      </c>
+      <c r="L78" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="N78" t="n">
+        <v>41</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" t="n">
+        <v>337554287</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>141</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>['Drama', 'Comedy']</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>['Beijing Enlight Pictures']</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="b">
+        <v>0</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>/yfQXs8yXplCVXTLi9mxgvRf4ymE.jpg</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>[18, 878, 28, 12, 53, 10752]</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>695721</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>The Hunger Games: The Ballad of Songbirds &amp; Snakes</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Años antes de convertirse en el tiránico Presidente de Panem, el Coriolanus Snow de 18 años es la última esperanza de su desvaneciente linaje, la una vez orgullosa familia que había caído en desgracia en un Capitolio post-guerra. Con los décimos Juegos del Hambre aproximándose rápidamente, el joven Snow se sorprende cuando es asignado como mentor de Lucy Gray Baird, la niña tributo del empobrecido Distrito 12. Pero luego de que Lucy Gray consigue toda la atención de Panem al cantar desafiante durante la ceremonia de la cosecha, Snow piensa que podría dar vuelta su suerte. Uniendo sus instintos de espectáculo y de encontrada astucia política, la carrera de Snow y Lucy Gray para sobrevivir revelerá quién es un pájaro cantor, y quién es una víbora.</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>54.722</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>/lQS3Owbte49Mkz5nFach4UgSZDF.jpg</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>2023-11-15</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Los juegos del hambre: La balada de pájaros cantores y serpientes</t>
+        </is>
+      </c>
+      <c r="L79" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" t="n">
+        <v>7</v>
+      </c>
+      <c r="N79" t="n">
+        <v>2912</v>
+      </c>
+      <c r="O79" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="P79" t="n">
+        <v>337371917</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>157</v>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>['Drama', 'Science Fiction', 'Action', 'Adventure', 'Thriller', 'War']</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>['Lionsgate', 'Color Force', 'about:blank', 'Studio Babelsberg']</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>https://hungergames.movie/</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Everyone hungers for something.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="b">
+        <v>0</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>/T6MfrCWpEyDOpbNqILFT6MHxb3.jpg</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>[9648, 80, 53]</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1108211</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>消失的她</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>11.419</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>/v4nkWUusA5tBNDfavvXfnw0mOWS.jpg</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>2023-06-22</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>消失的她</t>
+        </is>
+      </c>
+      <c r="L80" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N80" t="n">
+        <v>83</v>
+      </c>
+      <c r="O80" t="n">
+        <v>9500000</v>
+      </c>
+      <c r="P80" t="n">
+        <v>334039200</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>122</v>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>['Mystery', 'Crime', 'Thriller']</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>['Tao Piao Piao', 'As One Production']</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>['English', '普通话']</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="b">
+        <v>0</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>/rOJb0yQOCny0bPjg8bCLw8DyAD7.jpg</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>[35, 12, 878]</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>550988</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Free Guy</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Un hombre descubre que en realidad es un personaje dentro de un videojuego. Guy (Ryan Reynolds) trabaja como cajero de un banco, es un tipo alegre y solitario al que nada la amarga el día. Incluso si le utilizan como rehén durante un atraco a su banco, él sigue sonriendo como si nada. Pero un día se da cuenta de que Free City no es exactamente la ciudad que él creía. Guy va a descubrir que en realidad es un personaje no jugable dentro de un brutal videojuego. Ahora que sabe que es un personaje de videojuego, Guy, acompañado por Molotov Girl (Jodie Comer), decidirá enfrentarse a todos los villanos que asolan la ciudad.</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>70.52200000000001</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>/suaooqn1Mnv60V19MoGxneMupJs.jpg</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>2021-08-11</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Free Guy: Tomando el Control</t>
+        </is>
+      </c>
+      <c r="L81" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8958</v>
+      </c>
+      <c r="O81" t="n">
+        <v>110000000</v>
+      </c>
+      <c r="P81" t="n">
+        <v>331526598</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>115</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>['Comedy', 'Adventure', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>['Berlanti Productions', '21 Laps Entertainment', 'Maximum Effort', 'Lit Entertainment Group', '20th Century Studios']</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>https://www.20thcenturystudios.com/movies/free-guy</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Life's too short to be a background character.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="b">
+        <v>0</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>/mQZJoIhTEkNhCYAqcHrQqhENLdu.jpg</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>[16, 878, 10751]</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1184918</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>The Wild Robot</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Un robot - ROZZUM unidad 7134, "Roz" para abreviar - naufraga en una isla deshabitada y debe aprender a adaptarse al duro entorno, estableciendo gradualmente relaciones con los animales de la isla y convirtiéndose en la madre adoptiva de un ganso huérfano.</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>392.874</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>/a0a7RC01aTa7pOnskgJb3mCD2Ba.jpg</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>2024-09-12</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Robot salvaje</t>
+        </is>
+      </c>
+      <c r="L82" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="N82" t="n">
+        <v>4411</v>
+      </c>
+      <c r="O82" t="n">
+        <v>78000000</v>
+      </c>
+      <c r="P82" t="n">
+        <v>324816010</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>102</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>['Animation', 'Science Fiction', 'Family']</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>['DreamWorks Animation']</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>https://www.thewildrobotmovie.com</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Discover your true nature.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="b">
+        <v>0</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>/4tdV5AeojEdbvn6VpeQrbuDlmzs.jpg</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>[16, 18, 12, 14]</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>916224</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>すずめの戸締まり</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sin saberlo, le abrió las puertas al caos. Ahora, Suzume, una chica de diecisiete años, trabaja codo a codo con un misterioso aliado para evitar que Japón sufra más calamidades.</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>/iUfWPVyuLA4wZ5EetHyyGsi25SF.jpg</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>2022-11-11</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Suzume</t>
+        </is>
+      </c>
+      <c r="L83" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="N83" t="n">
+        <v>1406</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0</v>
+      </c>
+      <c r="P83" t="n">
+        <v>323638107</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>121</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>['Animation', 'Drama', 'Adventure', 'Fantasy']</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>['CoMix Wave Films', 'Story', 'Lawson Entertainment', 'jeki', 'voque ting', 'KADOKAWA', 'Aniplex', 'TOHO']</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>['English', '日本語']</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>https://www.suzume-movie.com</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>On the other side of the door, was time in its entirety.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="b">
+        <v>0</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>/stmYfCUGd8Iy6kAMBr6AmWqx8Bq.jpg</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>[28, 878, 35, 10751]</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>454626</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Sonic the Hedgehog</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tom Wachowski, el sheriff de la ciudad de Green Hills, viajará a San Francisco para ayudar a Sonic, un erizo azul antropomórfico que corre a velocidades supersónicas, en su batalla contra el maligno Dr. Robotnik y sus aliados.</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>125.716</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>/rK25c71fYVi0Bv7RrTChK7NAQjC.jpg</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Sonic: La Película</t>
+        </is>
+      </c>
+      <c r="L84" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" t="n">
+        <v>7.308</v>
+      </c>
+      <c r="N84" t="n">
+        <v>9794</v>
+      </c>
+      <c r="O84" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="P84" t="n">
+        <v>319715683</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>99</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>['Action', 'Science Fiction', 'Comedy', 'Family']</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>['Original Film', 'Blur Studio', 'Marza Animation Planet', 'Paramount Pictures', 'SEGA', 'SEGA of America']</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>https://www.paramountmovies.com/movies/sonic-the-hedgehog</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>A whole new speed of hero.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="b">
+        <v>0</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>/gklkxY0veMajdCiGe6ggsh07VG2.jpg</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>[16, 12, 35, 10751]</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>940551</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Migration</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Después de que una familia de patos migratorios aterriza en su estanque con emocionantes historias de lugares remotos, la familia Mallard embarca en un viaje familiar, atravezando la ciudad de Nueva York, con destino a la tropical Jamaica.</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>129.739</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>/diEeiB2DmZZadHISkg24RO2n0rT.jpg</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>2023-12-06</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>¡Patos!</t>
+        </is>
+      </c>
+      <c r="L85" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" t="n">
+        <v>7.411</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1945</v>
+      </c>
+      <c r="O85" t="n">
+        <v>72000000</v>
+      </c>
+      <c r="P85" t="n">
+        <v>298776052</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>83</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>['Animation', 'Adventure', 'Comedy', 'Family']</t>
+        </is>
+      </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>['Universal Pictures', 'Illumination']</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>https://www.migration.movie</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Odd ducks welcome.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="b">
+        <v>0</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>/AsqUSUqXrK8JfH8WEQnCXVbIAv6.jpg</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>[878, 53, 27]</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>520763</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>A Quiet Place Part II</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>La familia Abbott ahora se enfrenta a los terrores del mundo exterior. Forzados a aventurarse en lo desconocido, se dan cuenta de que las criaturas que cazan por el sonido no son las únicas amenazas que acechan más allá del camino de arena.</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>48.729</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>/6uRb5axnwAd17h4ak4ENHcJqHVr.jpg</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>2021-05-21</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Un lugar en silencio: Parte II</t>
+        </is>
+      </c>
+      <c r="L86" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N86" t="n">
+        <v>6686</v>
+      </c>
+      <c r="O86" t="n">
+        <v>55000000</v>
+      </c>
+      <c r="P86" t="n">
+        <v>297372261</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>96</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>['Science Fiction', 'Thriller', 'Horror']</t>
+        </is>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>['Paramount Pictures', 'Platinum Dunes', 'Sunday Night Productions']</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>https://www.aquietplacemovie.com</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Silence is not enough.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="b">
+        <v>0</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>/gGgDMV1vN20q8qEdxV0K43UrK0y.jpg</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>[27, 9648, 53]</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>507089</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Five Nights at Freddy's</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Un guardia de seguridad con problemas comienza a trabajar en Freddy Fazbear's Pizza. Mientras pasa su primera noche en el trabajo, se da cuenta de que el turno de noche en Freddy's no será tan fácil de superar.</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>82.565</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>/t6RSJ1z8bDEYpk4fLwxfkXciUak.jpg</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>2023-10-25</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Five Nights at Freddy's</t>
+        </is>
+      </c>
+      <c r="L87" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="N87" t="n">
+        <v>4240</v>
+      </c>
+      <c r="O87" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="P87" t="n">
+        <v>297144130</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>110</v>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>['Horror', 'Mystery', 'Thriller']</t>
+        </is>
+      </c>
+      <c r="S87" t="inlineStr">
+        <is>
+          <t>['Blumhouse Productions', 'Scott Cawthon Productions']</t>
+        </is>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>https://www.fivenightsatfreddys.movie</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Can you survive five nights?</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="b">
+        <v>0</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>/ybn3jCia5XBD0ZgEM07gcUPuRNh.jpg</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>[16, 12, 14, 10751, 18]</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>508883</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>君たちはどう生きるか</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Mientras la Segunda Guerra Mundial hace estragos, el adolescente Mahito, atormentado por la trágica muerte de su madre, es trasladado de Tokio a la serena casa rural de su nueva madrastra Natsuko, una mujer que tiene un sorprendente parecido con la madre del niño. Mientras intenta adaptarse, este nuevo y extraño mundo se vuelve aún más extraño tras la aparición de una persistente garza real, que deja perplejo y atormenta a Mahito, llamándolo "el tan esperado".</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>72.075</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>/kUT2nTjJfccfmpoOG4sUWmHyCZY.jpg</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>2023-07-14</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>El niño y la garza</t>
+        </is>
+      </c>
+      <c r="L88" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N88" t="n">
+        <v>2036</v>
+      </c>
+      <c r="O88" t="n">
+        <v>50000000</v>
+      </c>
+      <c r="P88" t="n">
+        <v>294200000</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>124</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>['Animation', 'Adventure', 'Fantasy', 'Family', 'Drama']</t>
+        </is>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>['Studio Ghibli']</t>
+        </is>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>['日本語']</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>https://gkids.com/films/the-boy-and-the-heron/</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Where death comes to an end, life finds a new beginning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="b">
+        <v>0</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>/xyS0NgcQ2pbGWcwvSSu3xKEBhoO.jpg</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>[18, 10402, 36]</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>614934</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Elvis</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>La película explora la vida y la música de Elvis Presley a través del prisma de su relación con el coronel Tom Parker, su enigmático manager. La historia profundiza en la compleja dinámica que existía entre Presley y Parker que abarca más de 20 años, desde el ascenso de Presley a la fama hasta su estrellato sin precedentes, en el contexto de la revolución cultural y la pérdida de la inocencia en Estados Unidos. Y en el centro de ese periplo está Priscilla Presley (Olivia DeJonge), una de las personas más importantes e influyentes en la vida de Elvis.</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>34.553</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>/z4miRBGEqhkIkUr0ausHLfUytgq.jpg</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>2022-06-22</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Elvis</t>
+        </is>
+      </c>
+      <c r="L89" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N89" t="n">
+        <v>3496</v>
+      </c>
+      <c r="O89" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="P89" t="n">
+        <v>288670284</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>159</v>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>['Drama', 'Music', 'History']</t>
+        </is>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>['Warner Bros. Pictures', 'Bazmark', 'The Jackal Group']</t>
+        </is>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>https://elvis.warnerbros.com</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>The Man. The Legend. The King of Rock &amp; Roll.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="b">
+        <v>0</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>/zUmEx2kHpaF9UXKXhc3TUx51qUm.jpg</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>[16, 35, 878, 10751]</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1228564</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>熊出没·逆转时空</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>/K785l6QmXaulFqo8Judi65nHK8.jpg</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>2024-02-10</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>熊出没·逆转时空</t>
+        </is>
+      </c>
+      <c r="L90" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N90" t="n">
+        <v>8</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>275815986</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>105</v>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>['Animation', 'Comedy', 'Science Fiction', 'Family']</t>
+        </is>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>['Fantawild Animation']</t>
+        </is>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>The bears are back in time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="b">
+        <v>0</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>/5i6SjyDbDWqyun8klUuCxrlFbyw.jpg</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>[18, 28]</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>677179</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Creed III</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Adonis Creed ya ha llegado a la cima de su carrera y no tiene nada más que demostrar en el mundo del boxeo. Convertido en un ídolo de este boxeo pasa sus días rodeado de su familia y seres queridos. Sin embargo, todo cambiará cuando regrese un fantasma de su infancia. Su amigo de juventud, Damián, acaba de salir de la cárcel y desea demostrar todo lo que ha aprendido de boxeo estos años. Por ello, querrá enfrentarse en el cuadrilátero con su antiguo amigo.  Adonis Creed tendrá que enfrentarse a este adversario, que no solo quiere quitarle su título de boxeador, sino que desea acabar con él.</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>45.461</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>/fcFMd3HdyX7r5gtFwVnn2qr5Yhq.jpg</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>2023-03-01</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Creed III</t>
+        </is>
+      </c>
+      <c r="L91" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" t="n">
+        <v>7.116</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2584</v>
+      </c>
+      <c r="O91" t="n">
+        <v>75000000</v>
+      </c>
+      <c r="P91" t="n">
+        <v>275300000</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>116</v>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>['Drama', 'Action']</t>
+        </is>
+      </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>['Metro-Goldwyn-Mayer', 'Chartoff-Winkler Productions', 'Proximity Media', 'Outlier Society']</t>
+        </is>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>['English', 'Español']</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>https://www.mgmstudios.com/creed-iii</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>You can't run from your past.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="b">
+        <v>0</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>/yF1eOkaYvwiORauRCPWznV9xVvi.jpg</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>[12, 28, 878]</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>298618</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>The Flash</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Cuando su intento de salvar a su familia altera el futuro sin darse cuenta, Barry Allen queda atrapado en una realidad en la que el general Zod ha regresado y no hay superhéroes a los que recurrir. En última instancia, para salvar el mundo en el que se encuentra y regresar al futuro que conoce, la única esperanza de Barry es escapar de él para salvar su vida. Pero, ¿será suficiente hacer el último sacrificio para reiniciar el universo?</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>69.086</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>/x9Qc86JEyYkAKsdzjDpS5kbaAB7.jpg</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>2023-06-13</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Flash</t>
+        </is>
+      </c>
+      <c r="L92" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="N92" t="n">
+        <v>4418</v>
+      </c>
+      <c r="O92" t="n">
+        <v>220000000</v>
+      </c>
+      <c r="P92" t="n">
+        <v>271333313</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>144</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>['Adventure', 'Action', 'Science Fiction']</t>
+        </is>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>['Warner Bros. Pictures', 'Double Dream', 'The Disco Factory', 'DC Films']</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>['English', 'Español', 'Pусский']</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>https://www.dc.com/theflash</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Worlds collide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="b">
+        <v>0</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>/aX3Od8NVLgM7pMYgRpTPkwSrbSC.jpg</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>[27]</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>968051</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>The Nun II</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1956 – Francia. Un sacerdote es asesinado. Un mal se está extendiendo. La hermana Irene una vez más se encuentra cara a cara con Valak, la monja demonio.</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>66.733</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>/x0ryPlzZjpOojEAuGrre2lFuBv6.jpg</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>2023-09-06</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>La monja II</t>
+        </is>
+      </c>
+      <c r="L93" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" t="n">
+        <v>6.714</v>
+      </c>
+      <c r="N93" t="n">
+        <v>2122</v>
+      </c>
+      <c r="O93" t="n">
+        <v>38500000</v>
+      </c>
+      <c r="P93" t="n">
+        <v>269670590</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>110</v>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>['Horror']</t>
+        </is>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>['New Line Cinema', 'Atomic Monster', 'The Safran Company']</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>['Español', 'English', 'Italiano', 'Português', 'Français']</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>https://www.warnerbros.com/movies/nun2</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Confess your sins.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="b">
+        <v>0</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>/6XjMwQTvnICBz6TguiDKkDVHvgS.jpg</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>[27, 878, 53]</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>762441</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>A Quiet Place: Day One</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Mientras la ciudad de Nueva York es invadida por criaturas alienígenas que cazan mediante el sonido, una mujer llamada Sammy lucha por sobrevivir.</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>117.917</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>/6efQJ7pu9GPketUDBAhJtgZLkvD.jpg</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Un lugar en silencio: Día uno</t>
+        </is>
+      </c>
+      <c r="L94" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" t="n">
+        <v>6.745</v>
+      </c>
+      <c r="N94" t="n">
+        <v>2560</v>
+      </c>
+      <c r="O94" t="n">
+        <v>67000000</v>
+      </c>
+      <c r="P94" t="n">
+        <v>261907653</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>99</v>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>['Horror', 'Science Fiction', 'Thriller']</t>
+        </is>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>['Paramount Pictures', 'Platinum Dunes', 'Sunday Night Productions']</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>https://www.aquietplacemovie.com</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Hear how it all began.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="b">
+        <v>0</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>/uRKhh7JYMD6QWNt0NjmMfh7uLdm.jpg</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>[10402]</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>1160164</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>TAYLOR SWIFT | THE ERAS TOUR</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>¡El fenómeno cultural continúa en la pantalla grande! Sumérgete en esta experiencia cinematográfica de concierto única en la vida con una vista cinematográfica impresionante de la gira histórica.</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>31.541</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>/tQfweKh2gKuTVNLm1AZCnB3VDQE.jpg</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Taylor Swift: The Eras Tour</t>
+        </is>
+      </c>
+      <c r="L95" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="N95" t="n">
+        <v>436</v>
+      </c>
+      <c r="O95" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="P95" t="n">
+        <v>261656269</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>169</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>['Music']</t>
+        </is>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>['Taylor Swift Productions', 'Silent House Productions']</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>https://www.tstheerastourfilm.com</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>It's been a long time coming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="b">
+        <v>0</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>/3G1Q5xF40HkUBJXxt2DQgQzKTp5.jpg</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>[16, 35, 10751, 14]</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>568124</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Encanto</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Encanto relata la historia de una familia extraordinaria; los Madrigal, quienes viven escondidos en las montañas de Colombia, en una casa mágica, un pueblo vibrante y en un lugar maravilloso llamado Encanto. La magia del Encanto ha bendecido a cada niño de la familia con un don único, desde la superfuerza hasta el poder de sanar; a todos, excepto Mirabel, quien desea ser tan especial como el resto de su familia.  Pero cuando la magia que rodea al Encanto está en peligro, Mirabel decide que ella, la única Madrigal sin ningún tipo de don único, puede ser la única esperanza de su excepcional familia.</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>88.952</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>/d0ezQ1Jz0lpNsX1skEmIvqRL7mN.jpg</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>2021-10-13</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Encanto</t>
+        </is>
+      </c>
+      <c r="L96" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" t="n">
+        <v>7.594</v>
+      </c>
+      <c r="N96" t="n">
+        <v>9616</v>
+      </c>
+      <c r="O96" t="n">
+        <v>135000000</v>
+      </c>
+      <c r="P96" t="n">
+        <v>261289554</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>102</v>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>['Animation', 'Comedy', 'Family', 'Fantasy']</t>
+        </is>
+      </c>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>['Walt Disney Animation Studios', 'Walt Disney Pictures']</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>['English', 'Español']</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/encanto</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>There's a little magic in all of us...almost all of us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="b">
+        <v>0</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>/rBgzI1a126JWA7YJd7p1NBmC61z.jpg</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>[16, 35, 18]</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>783675</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>THE FIRST SLAM DUNK</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Ryota Miyagi, un jugador inteligente y veloz, se une al equipo de baloncesto de Shohoku, donde compite junto a Sakuragi, Rukawa, Akagi y Mitsui en el campeonato nacional. Su próximo desafío: enfrentarse al campeón defensor, el instituto Sannoh Kogyo.</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>20.243</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>/pWVJqFFeKBH3bp9szlNJpoHQFxt.jpg</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>2022-12-03</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Slam Dunk: La Película</t>
+        </is>
+      </c>
+      <c r="L97" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" t="n">
+        <v>7.787</v>
+      </c>
+      <c r="N97" t="n">
+        <v>422</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0</v>
+      </c>
+      <c r="P97" t="n">
+        <v>258000000</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>125</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>['Animation', 'Comedy', 'Drama']</t>
+        </is>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>['Toei Animation', 'Toei Company', 'DandeLion Animation Studio']</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>['日本語']</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>http://gkids.com/films/the-first-slam-dunk/</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>17 years and... 40 minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="b">
+        <v>0</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>/ehumsuIBbgAe1hg343oszCLrAfI.jpg</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>[16, 10751, 14, 12]</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>1022796</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Wish</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Asha y una pequeña bola de energía ilimitada llamada Star demuestran que cuando la voluntad de un ser humano valiente se conecta con la magia de las estrellas, pueden suceder cosas maravillosas.</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>82.961</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>/1VXMrUioKfPAPSsezHKexx77Dbz.jpg</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>2023-11-13</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Wish: El poder de los deseos</t>
+        </is>
+      </c>
+      <c r="L98" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1559</v>
+      </c>
+      <c r="O98" t="n">
+        <v>175000000</v>
+      </c>
+      <c r="P98" t="n">
+        <v>254997360</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>95</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>['Animation', 'Family', 'Fantasy', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>['Walt Disney Pictures', 'Walt Disney Animation Studios']</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>https://movies.disney.com/wish</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Be careful what you wish for.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="b">
+        <v>0</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>/P82NAcEsLIYgQtrtn36tYsj41m.jpg</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>[16, 35, 10751, 12]</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>748783</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>The Garfield Movie</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Garfield, el famoso gato que odia los lunes y es amante de la lasaña, está a punto de vivir una salvaje aventura al aire libre. Tras un inesperado reencuentro con su padre, el desaliñado gato callejero Vic, Garfield y su amigo canino Odie se ven obligados a abandonar su mimada vida para unirse a Vic en un divertidísimo atraco de alto riesgo.</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>153.942</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>/tkdc73JiPVvzngSpbLEIfFNjll1.jpg</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>2024-04-30</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Garfield: Fuera de casa</t>
+        </is>
+      </c>
+      <c r="L99" t="b">
+        <v>0</v>
+      </c>
+      <c r="M99" t="n">
+        <v>7.086</v>
+      </c>
+      <c r="N99" t="n">
+        <v>1218</v>
+      </c>
+      <c r="O99" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="P99" t="n">
+        <v>254907482</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>100</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>['Animation', 'Comedy', 'Family', 'Adventure']</t>
+        </is>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>['Alcon Entertainment', 'DNEG', 'Wayfarer Studios', 'One Cool Group', 'Stage 6 Films', 'Andrews McMeel Entertainment', 'John Cohen Productions']</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>['English']</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>https://www.thegarfield-movie.com/</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Indoor cat. Outdoor adventure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="b">
+        <v>0</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>/jDJ8iCLMBLhoznsXh9SEjpnQCdx.jpg</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>[18]</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>945664</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>人生大事</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Habiendo sido puesto en libertad después de cumplir su condena, un director de una funeraria se cruza accidentalmente con una chica, lo que provoca un cambio inesperado en su actitud ante la vida.</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>5.936</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>/bAuR2fjqtuI5uxpJiamUhP3KrzS.jpg</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>2022-06-24</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>人生大事</t>
+        </is>
+      </c>
+      <c r="L100" t="b">
+        <v>0</v>
+      </c>
+      <c r="M100" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="N100" t="n">
+        <v>37</v>
+      </c>
+      <c r="O100" t="n">
+        <v>8800000</v>
+      </c>
+      <c r="P100" t="n">
+        <v>253816909</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>112</v>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>['Drama']</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>['Lian Ray Pictures', 'Zhejiang Hengdian Film Production', 'China Film Group Corporation', 'Tianjin Maoyan Weiying Culture Media', 'Tao Piao Piao', 'Weibo Corporation']</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="b">
+        <v>0</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>/zXyYAcZmTh1l6jaJzl8cxP5NN9P.jpg</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>[16, 36]</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1089654</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>zh</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>长安三万里</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>/7wxk8Ka5AGUIjCpEPg4vBOwSSul.jpg</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>2023-07-02</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Chang 'An</t>
+        </is>
+      </c>
+      <c r="L101" t="b">
+        <v>0</v>
+      </c>
+      <c r="M101" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="N101" t="n">
+        <v>47</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="n">
+        <v>252520750</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>169</v>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>['Animation', 'History']</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>['Light Chaser Animation Studios']</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>['普通话']</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
